--- a/vessel_counting_072026.xlsx
+++ b/vessel_counting_072026.xlsx
@@ -8,22 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jainglobalcom-my.sharepoint.com/personal/luiscarlos_gaitan_jainglobal_com/Documents/Coding/vessel_crossing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3888" documentId="8_{ACBAE674-F7E3-4718-8201-9F85458D862D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7CC63B4-5CC8-4AD9-B0D0-C5326DA6BC60}"/>
+  <xr:revisionPtr revIDLastSave="4067" documentId="8_{ACBAE674-F7E3-4718-8201-9F85458D862D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B44F0F5E-E490-4285-A0C5-BFAF3946E630}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="20235" yWindow="4800" windowWidth="23100" windowHeight="17145" xr2:uid="{AD02B413-0D1C-4968-9BB9-B945211DCBC0}"/>
+    <workbookView minimized="1" xWindow="2595" yWindow="2595" windowWidth="43200" windowHeight="17145" activeTab="1" xr2:uid="{AD02B413-0D1C-4968-9BB9-B945211DCBC0}"/>
   </bookViews>
   <sheets>
     <sheet name="SoH" sheetId="1" r:id="rId1"/>
-    <sheet name="bab" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId4"/>
-    <sheet name="Sheet3" sheetId="5" r:id="rId5"/>
-    <sheet name="entries" sheetId="6" r:id="rId6"/>
-    <sheet name="mapping" sheetId="7" r:id="rId7"/>
+    <sheet name="Sheet4" sheetId="8" r:id="rId2"/>
+    <sheet name="bab" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId5"/>
+    <sheet name="Sheet3" sheetId="5" r:id="rId6"/>
+    <sheet name="entries" sheetId="6" r:id="rId7"/>
+    <sheet name="mapping" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">entries!$B$1:$AD$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SoH!$B$2:$N$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">entries!$B$1:$AD$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">SoH!$B$2:$N$71</definedName>
     <definedName name="afra_scale">Table1[#All]</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -51,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2301" uniqueCount="529">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2343" uniqueCount="543">
   <si>
     <t>vessel_name</t>
   </si>
@@ -1568,9 +1569,6 @@
     <t>Al Rayyan</t>
   </si>
   <si>
-    <t>Rayyan</t>
-  </si>
-  <si>
     <t>PANAMA PROSPERITY</t>
   </si>
   <si>
@@ -1638,6 +1636,51 @@
   </si>
   <si>
     <t>not in kpler</t>
+  </si>
+  <si>
+    <t>ME</t>
+  </si>
+  <si>
+    <t>SEA V</t>
+  </si>
+  <si>
+    <t>SINGAPORE PROSPERITY</t>
+  </si>
+  <si>
+    <t>ALGERIA PROSPERITY</t>
+  </si>
+  <si>
+    <t>FUJAIRAH</t>
+  </si>
+  <si>
+    <t>IRAQ</t>
+  </si>
+  <si>
+    <t>SOHAR</t>
+  </si>
+  <si>
+    <t>Loading country</t>
+  </si>
+  <si>
+    <t>destination</t>
+  </si>
+  <si>
+    <t>tanker name</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>1,986,831</t>
+  </si>
+  <si>
+    <t>1,959,999</t>
+  </si>
+  <si>
+    <t>2,000,002</t>
+  </si>
+  <si>
+    <t>UAE</t>
   </si>
 </sst>
 </file>
@@ -1968,7 +2011,7 @@
     <c:title>
       <c:tx>
         <c:strRef>
-          <c:f>SoH!$S$126</c:f>
+          <c:f>SoH!$S$130</c:f>
           <c:strCache>
             <c:ptCount val="1"/>
             <c:pt idx="0">
@@ -2028,7 +2071,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>SoH!$S$135:$S$159</c:f>
+              <c:f>SoH!$S$139:$S$163</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="25"/>
@@ -2104,12 +2147,15 @@
                 <c:pt idx="23">
                   <c:v>46237</c:v>
                 </c:pt>
+                <c:pt idx="24">
+                  <c:v>46238</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>SoH!$T$135:$T$159</c:f>
+              <c:f>SoH!$T$139:$T$163</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"??_-;_-@_-</c:formatCode>
                 <c:ptCount val="25"/>
@@ -2184,6 +2230,9 @@
                 </c:pt>
                 <c:pt idx="23">
                   <c:v>5000</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2437,7 +2486,7 @@
     <c:title>
       <c:tx>
         <c:strRef>
-          <c:f>SoH!$S$164</c:f>
+          <c:f>SoH!$S$168</c:f>
           <c:strCache>
             <c:ptCount val="1"/>
             <c:pt idx="0">
@@ -2487,7 +2536,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>SoH!$U$166</c:f>
+              <c:f>SoH!$U$170</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2508,7 +2557,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>SoH!$S$167:$S$190</c:f>
+              <c:f>SoH!$S$171:$S$194</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="24"/>
@@ -2586,7 +2635,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>SoH!$U$167:$U$190</c:f>
+              <c:f>SoH!$U$171:$U$194</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
@@ -2673,7 +2722,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>SoH!$V$166</c:f>
+              <c:f>SoH!$V$170</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2694,7 +2743,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>SoH!$S$167:$S$190</c:f>
+              <c:f>SoH!$S$171:$S$194</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="24"/>
@@ -2772,7 +2821,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>SoH!$V$167:$V$190</c:f>
+              <c:f>SoH!$V$171:$V$194</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="24"/>
@@ -3128,7 +3177,7 @@
     <c:title>
       <c:tx>
         <c:strRef>
-          <c:f>SoH!$S$164</c:f>
+          <c:f>SoH!$S$168</c:f>
           <c:strCache>
             <c:ptCount val="1"/>
             <c:pt idx="0">
@@ -3178,7 +3227,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>SoH!$W$166</c:f>
+              <c:f>SoH!$W$170</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3199,7 +3248,7 @@
           <c:invertIfNegative val="0"/>
           <c:cat>
             <c:numRef>
-              <c:f>SoH!$S$167:$S$188</c:f>
+              <c:f>SoH!$S$171:$S$192</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="22"/>
@@ -3274,7 +3323,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>SoH!$W$167:$W$190</c:f>
+              <c:f>SoH!$W$171:$W$194</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"??_-;_-@_-</c:formatCode>
                 <c:ptCount val="24"/>
@@ -3376,7 +3425,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>SoH!$X$166</c:f>
+              <c:f>SoH!$X$170</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -3399,7 +3448,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>SoH!$S$167:$S$188</c:f>
+              <c:f>SoH!$S$171:$S$192</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yyyy</c:formatCode>
                 <c:ptCount val="22"/>
@@ -3474,7 +3523,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>SoH!$Y$167:$Y$188</c:f>
+              <c:f>SoH!$Y$171:$Y$192</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0_-;\-* #,##0_-;_-* "-"??_-;_-@_-</c:formatCode>
                 <c:ptCount val="22"/>
@@ -6579,13 +6628,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>514349</xdr:colOff>
-      <xdr:row>133</xdr:row>
+      <xdr:row>137</xdr:row>
       <xdr:rowOff>61912</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>657224</xdr:colOff>
-      <xdr:row>159</xdr:row>
+      <xdr:row>163</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6615,13 +6664,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>162</xdr:row>
+      <xdr:row>166</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>619125</xdr:colOff>
-      <xdr:row>188</xdr:row>
+      <xdr:row>192</xdr:row>
       <xdr:rowOff>14288</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -6653,13 +6702,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>192</xdr:row>
+      <xdr:row>196</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>217</xdr:row>
+      <xdr:row>221</xdr:row>
       <xdr:rowOff>147638</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -7064,7 +7113,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D528AF1-A5E7-4779-9634-4965A885E745}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:AJ189"/>
+  <dimension ref="A1:AJ193"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="22.7109375" bestFit="1" customWidth="1"/>
@@ -7926,7 +7975,7 @@
       <c r="M23" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="P23" t="s">
+      <c r="P23" s="11" t="s">
         <v>181</v>
       </c>
       <c r="U23" s="5"/>
@@ -8265,9 +8314,6 @@
       <c r="M32" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="P32" t="s">
-        <v>181</v>
-      </c>
       <c r="R32" t="s">
         <v>33</v>
       </c>
@@ -8291,7 +8337,7 @@
         <v>24</v>
       </c>
       <c r="H33" s="11">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I33" s="11"/>
       <c r="J33" s="11" t="s">
@@ -8461,9 +8507,6 @@
       <c r="M40" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="P40" t="s">
-        <v>181</v>
-      </c>
     </row>
     <row r="41" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B41" s="11" t="s">
@@ -8501,9 +8544,7 @@
       <c r="N41" t="s">
         <v>343</v>
       </c>
-      <c r="P41" t="s">
-        <v>181</v>
-      </c>
+      <c r="P41" s="11"/>
     </row>
     <row r="42" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B42" s="11" t="s">
@@ -8525,7 +8566,7 @@
         <v>94</v>
       </c>
       <c r="H42" s="11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I42" s="11"/>
       <c r="J42" s="11" t="s">
@@ -8541,7 +8582,7 @@
       <c r="N42" t="s">
         <v>427</v>
       </c>
-      <c r="P42" t="s">
+      <c r="P42" s="11" t="s">
         <v>181</v>
       </c>
       <c r="R42" t="s">
@@ -8569,7 +8610,7 @@
         <v>24</v>
       </c>
       <c r="H43" s="11">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I43" s="11"/>
       <c r="J43" s="11" t="s">
@@ -8585,7 +8626,7 @@
       <c r="N43" t="s">
         <v>445</v>
       </c>
-      <c r="P43" t="s">
+      <c r="P43" s="11" t="s">
         <v>181</v>
       </c>
       <c r="U43" s="5"/>
@@ -8610,7 +8651,7 @@
         <v>20</v>
       </c>
       <c r="H44" s="11">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I44" s="11"/>
       <c r="J44" s="11" t="s">
@@ -8626,7 +8667,7 @@
       <c r="N44" t="s">
         <v>441</v>
       </c>
-      <c r="P44" t="s">
+      <c r="P44" s="11" t="s">
         <v>181</v>
       </c>
       <c r="U44" s="5"/>
@@ -8654,9 +8695,7 @@
       <c r="M45" s="11" t="s">
         <v>191</v>
       </c>
-      <c r="P45" t="s">
-        <v>181</v>
-      </c>
+      <c r="P45" s="11"/>
       <c r="U45" s="5"/>
     </row>
     <row r="46" spans="2:21" x14ac:dyDescent="0.25">
@@ -8713,7 +8752,7 @@
         <v>41</v>
       </c>
       <c r="H47" s="11">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="I47" s="11"/>
       <c r="J47" s="11" t="s">
@@ -8726,7 +8765,7 @@
       <c r="M47" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="P47" t="s">
+      <c r="P47" s="11" t="s">
         <v>181</v>
       </c>
       <c r="U47" s="5"/>
@@ -9000,9 +9039,6 @@
       <c r="M56" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="P56" t="s">
-        <v>181</v>
-      </c>
     </row>
     <row r="57" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B57" s="11" t="s">
@@ -9035,8 +9071,8 @@
       <c r="M57" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="P57" t="s">
-        <v>181</v>
+      <c r="S57">
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="2:21" x14ac:dyDescent="0.25">
@@ -9057,7 +9093,7 @@
         <v>24</v>
       </c>
       <c r="H58" s="11">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I58" s="11"/>
       <c r="J58" s="11" t="s">
@@ -9073,8 +9109,11 @@
       <c r="N58" t="s">
         <v>445</v>
       </c>
-      <c r="P58" t="s">
+      <c r="P58" s="11" t="s">
         <v>181</v>
+      </c>
+      <c r="S58">
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="2:21" x14ac:dyDescent="0.25">
@@ -9106,72 +9145,66 @@
       <c r="M59" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="P59" t="s">
-        <v>181</v>
+      <c r="S59">
+        <v>2500</v>
       </c>
     </row>
     <row r="60" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B60" s="6" t="s">
-        <v>503</v>
-      </c>
-      <c r="C60" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>504</v>
-      </c>
-      <c r="E60" s="7">
+      <c r="B60" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E60" s="12">
         <v>46237</v>
       </c>
-      <c r="F60" s="7">
-        <v>46246</v>
-      </c>
-      <c r="G60" s="6" t="s">
-        <v>505</v>
-      </c>
-      <c r="H60" s="6">
+      <c r="F60" s="12">
+        <v>46603</v>
+      </c>
+      <c r="G60" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H60" s="11">
         <v>7</v>
       </c>
-      <c r="I60" s="6"/>
-      <c r="J60" s="6" t="s">
+      <c r="I60" s="11"/>
+      <c r="J60" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="K60" s="6"/>
-      <c r="L60" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M60" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="P60" t="s">
-        <v>181</v>
-      </c>
-      <c r="S60" t="s">
-        <v>91</v>
+      <c r="K60" s="11"/>
+      <c r="L60" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="M60" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="S60">
+        <f>+S58*S59</f>
+        <v>17500</v>
       </c>
     </row>
     <row r="61" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B61" s="11" t="s">
-        <v>111</v>
+        <v>505</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="D61" s="11" t="s">
-        <v>23</v>
-      </c>
+        <v>506</v>
+      </c>
+      <c r="D61" s="11"/>
       <c r="E61" s="12">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="F61" s="12">
-        <v>46603</v>
+        <v>46608</v>
       </c>
       <c r="G61" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H61" s="11">
-        <v>7</v>
-      </c>
+      <c r="H61" s="11"/>
       <c r="I61" s="11"/>
       <c r="J61" s="11" t="s">
         <v>34</v>
@@ -9183,224 +9216,224 @@
       <c r="M61" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="P61" t="s">
+      <c r="N61" t="s">
+        <v>521</v>
+      </c>
+      <c r="P61" s="11" t="s">
         <v>181</v>
+      </c>
+      <c r="S61">
+        <f>+S60*S57</f>
+        <v>35000</v>
       </c>
     </row>
     <row r="62" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B62" s="11" t="s">
-        <v>506</v>
+        <v>451</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>507</v>
-      </c>
-      <c r="D62" s="11"/>
-      <c r="E62" s="12">
-        <v>46239</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E62" s="12"/>
       <c r="F62" s="12">
-        <v>46608</v>
+        <v>46243</v>
       </c>
       <c r="G62" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H62" s="11"/>
+      <c r="H62" s="11">
+        <v>6</v>
+      </c>
       <c r="I62" s="11"/>
       <c r="J62" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="K62" s="11"/>
+      <c r="K62" s="11" t="s">
+        <v>254</v>
+      </c>
       <c r="L62" s="11" t="s">
         <v>17</v>
       </c>
       <c r="M62" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="N62" t="s">
-        <v>522</v>
-      </c>
-      <c r="P62" t="s">
-        <v>181</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="P62" s="11"/>
     </row>
     <row r="63" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B63" s="11" t="s">
-        <v>451</v>
-      </c>
-      <c r="C63" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="D63" s="11" t="s">
+      <c r="B63" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="D63" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E63" s="12"/>
-      <c r="F63" s="12">
-        <v>46243</v>
-      </c>
-      <c r="G63" s="11" t="s">
+      <c r="E63" s="7"/>
+      <c r="F63" s="7">
+        <v>46242</v>
+      </c>
+      <c r="G63" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="H63" s="11">
+      <c r="H63" s="6">
         <v>5</v>
       </c>
-      <c r="I63" s="11"/>
-      <c r="J63" s="11" t="s">
+      <c r="I63" s="6"/>
+      <c r="J63" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="K63" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="L63" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="M63" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="P63" t="s">
-        <v>181</v>
+      <c r="K63" s="6"/>
+      <c r="L63" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M63" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="S63">
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B64" s="6" t="s">
-        <v>125</v>
+        <v>516</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E64" s="7"/>
+        <v>259</v>
+      </c>
+      <c r="E64" s="7">
+        <v>46240</v>
+      </c>
       <c r="F64" s="7">
-        <v>46242</v>
-      </c>
-      <c r="G64" s="6" t="s">
-        <v>24</v>
-      </c>
+        <v>46243</v>
+      </c>
+      <c r="G64" s="6"/>
       <c r="H64" s="6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I64" s="6"/>
       <c r="J64" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="K64" s="6"/>
+      <c r="K64" s="6" t="s">
+        <v>254</v>
+      </c>
       <c r="L64" s="6" t="s">
         <v>48</v>
       </c>
       <c r="M64" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="P64" t="s">
-        <v>181</v>
-      </c>
     </row>
     <row r="65" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B65" s="6" t="s">
-        <v>517</v>
-      </c>
-      <c r="C65" s="6" t="s">
+      <c r="B65" s="11" t="s">
+        <v>518</v>
+      </c>
+      <c r="C65" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="D65" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="E65" s="7">
-        <v>46240</v>
-      </c>
-      <c r="F65" s="7">
-        <v>46243</v>
-      </c>
-      <c r="G65" s="6"/>
-      <c r="H65" s="6">
-        <v>4</v>
-      </c>
-      <c r="I65" s="6"/>
-      <c r="J65" s="6" t="s">
+      <c r="D65" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="E65" s="12">
+        <v>46242</v>
+      </c>
+      <c r="F65" s="12">
+        <v>46244</v>
+      </c>
+      <c r="G65" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="H65" s="11"/>
+      <c r="I65" s="11"/>
+      <c r="J65" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="K65" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="L65" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M65" s="6" t="s">
-        <v>18</v>
+      <c r="K65" s="11"/>
+      <c r="L65" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="M65" s="11" t="s">
+        <v>42</v>
       </c>
       <c r="P65" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="66" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B66" s="11" t="s">
+      <c r="B66" s="6" t="s">
         <v>519</v>
       </c>
-      <c r="C66" s="11" t="s">
+      <c r="C66" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D66" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="E66" s="12">
-        <v>46242</v>
-      </c>
-      <c r="F66" s="12">
+      <c r="D66" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E66" s="7">
+        <v>46206</v>
+      </c>
+      <c r="F66" s="7">
+        <v>46247</v>
+      </c>
+      <c r="G66" s="6"/>
+      <c r="H66" s="6">
+        <v>5</v>
+      </c>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K66" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="L66" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M66" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P66" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="AF66" s="48"/>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="B67" s="11" t="s">
+        <v>522</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E67" s="12">
+        <v>46241</v>
+      </c>
+      <c r="F67" s="12">
         <v>46244</v>
       </c>
-      <c r="G66" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="H66" s="11">
-        <v>1</v>
-      </c>
-      <c r="I66" s="11"/>
-      <c r="J66" s="11" t="s">
+      <c r="G67" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H67" s="11"/>
+      <c r="I67" s="11"/>
+      <c r="J67" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="K66" s="11"/>
-      <c r="L66" s="11" t="s">
+      <c r="K67" s="11"/>
+      <c r="L67" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="M66" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="P66" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B67" s="6" t="s">
-        <v>520</v>
-      </c>
-      <c r="C67" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E67" s="7">
-        <v>46206</v>
-      </c>
-      <c r="F67" s="7">
-        <v>46247</v>
-      </c>
-      <c r="G67" s="6"/>
-      <c r="H67" s="6">
-        <v>3</v>
-      </c>
-      <c r="I67" s="6"/>
-      <c r="J67" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="K67" s="6" t="s">
-        <v>521</v>
-      </c>
-      <c r="L67" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M67" s="6" t="s">
-        <v>18</v>
+      <c r="M67" s="11" t="s">
+        <v>50</v>
       </c>
       <c r="P67" t="s">
         <v>181</v>
@@ -9409,19 +9442,19 @@
     </row>
     <row r="68" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B68" s="6" t="s">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>23</v>
       </c>
       <c r="E68" s="7">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="F68" s="7">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="G68" s="6" t="s">
         <v>24</v>
@@ -9438,243 +9471,202 @@
       <c r="M68" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="P68" t="s">
+      <c r="P68" s="6" t="s">
         <v>181</v>
       </c>
       <c r="AF68" s="48"/>
     </row>
-    <row r="69" spans="2:32" hidden="1" x14ac:dyDescent="0.25">
-      <c r="U69" s="5"/>
-    </row>
-    <row r="70" spans="2:32" hidden="1" x14ac:dyDescent="0.25">
-      <c r="U70" s="5"/>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="B69" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="C69" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="D69" s="6"/>
+      <c r="E69" s="7">
+        <v>46246</v>
+      </c>
+      <c r="F69" s="7"/>
+      <c r="G69" s="6"/>
+      <c r="H69" s="6"/>
+      <c r="I69" s="6"/>
+      <c r="J69" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K69" s="6"/>
+      <c r="L69" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M69" s="6" t="s">
+        <v>346</v>
+      </c>
+      <c r="P69" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q69">
+        <v>1000</v>
+      </c>
+      <c r="AF69" s="48"/>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="B70" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C70" s="6"/>
+      <c r="D70" s="6"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
+      <c r="G70" s="6"/>
+      <c r="H70" s="6"/>
+      <c r="I70" s="6"/>
+      <c r="J70" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K70" s="6"/>
+      <c r="L70" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M70" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P70" s="6"/>
+      <c r="AF70" s="48"/>
     </row>
     <row r="71" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="U71" s="5"/>
+      <c r="B71" s="6" t="s">
+        <v>530</v>
+      </c>
+      <c r="C71" s="6"/>
+      <c r="D71" s="6"/>
+      <c r="E71" s="7"/>
+      <c r="F71" s="7"/>
+      <c r="G71" s="6"/>
+      <c r="H71" s="6"/>
+      <c r="I71" s="6"/>
+      <c r="J71" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K71" s="6"/>
+      <c r="L71" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M71" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P71" s="6"/>
+      <c r="AF71" s="48"/>
     </row>
     <row r="72" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B72" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C72" s="4" t="s">
+      <c r="B72" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="C72" s="6"/>
+      <c r="D72" s="6"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="7"/>
+      <c r="G72" s="6"/>
+      <c r="H72" s="6"/>
+      <c r="I72" s="6"/>
+      <c r="J72" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="K72" s="6"/>
+      <c r="L72" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M72" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="P72" s="6"/>
+      <c r="AF72" s="48"/>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="U73" s="5"/>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="U74" s="5"/>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.25">
+      <c r="B75" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C75" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D72" s="4" t="s">
+      <c r="D75" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="E72" s="4" t="s">
+      <c r="E75" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F72" s="4" t="s">
+      <c r="F75" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="G72" s="4" t="s">
+      <c r="G75" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H72" s="4" t="s">
+      <c r="H75" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I72" s="4" t="s">
+      <c r="I75" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J72" s="4" t="s">
+      <c r="J75" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="K72" s="4" t="s">
+      <c r="K75" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="L72" s="4" t="s">
+      <c r="L75" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M72" s="4" t="s">
+      <c r="M75" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="U72" s="5"/>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B73" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C73" s="9" t="s">
-        <v>114</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E73" s="10"/>
-      <c r="F73" s="10">
-        <v>46210</v>
-      </c>
-      <c r="G73" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H73" s="9"/>
-      <c r="I73" s="10">
-        <v>46218</v>
-      </c>
-      <c r="J73" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="K73" s="9"/>
-      <c r="L73" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M73" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="Q73" s="37">
-        <v>1000</v>
-      </c>
-      <c r="U73" s="5"/>
-      <c r="Y73">
-        <f>COUNTIFS(J:J,"in",L:L,AB73,H:H,"&gt;0")</f>
-        <v>14</v>
-      </c>
-      <c r="AB73" t="s">
-        <v>17</v>
-      </c>
-      <c r="AC73">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B74" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="C74" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E74" s="10">
-        <v>46211</v>
-      </c>
-      <c r="F74" s="10">
-        <v>46214</v>
-      </c>
-      <c r="G74" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H74" s="9"/>
-      <c r="I74" s="10">
-        <v>46217</v>
-      </c>
-      <c r="J74" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="K74" s="9" t="s">
-        <v>432</v>
-      </c>
-      <c r="L74" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M74" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q74" s="37">
-        <v>2000</v>
-      </c>
-      <c r="V74" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B75" s="9" t="s">
-        <v>101</v>
-      </c>
-      <c r="C75" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="D75" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E75" s="10"/>
-      <c r="F75" s="10">
-        <v>46209</v>
-      </c>
-      <c r="G75" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H75" s="9">
-        <v>2</v>
-      </c>
-      <c r="I75" s="10">
-        <v>46216</v>
-      </c>
-      <c r="J75" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="K75" s="9" t="s">
-        <v>196</v>
-      </c>
-      <c r="L75" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="M75" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q75" s="37">
-        <v>2000</v>
-      </c>
-      <c r="V75" t="s">
-        <v>196</v>
-      </c>
-      <c r="Y75">
-        <f>COUNTIFS(J:J,"in",L:L,AB75)</f>
-        <v>8</v>
-      </c>
-      <c r="AB75" t="s">
-        <v>48</v>
-      </c>
+      <c r="U75" s="5"/>
     </row>
     <row r="76" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B76" s="9" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C76" s="9" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E76" s="10">
-        <v>46209</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="E76" s="10"/>
       <c r="F76" s="10">
         <v>46210</v>
       </c>
       <c r="G76" s="9" t="s">
-        <v>110</v>
+        <v>20</v>
       </c>
       <c r="H76" s="9"/>
       <c r="I76" s="10">
-        <v>46215</v>
+        <v>46218</v>
       </c>
       <c r="J76" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K76" s="9" t="s">
-        <v>109</v>
-      </c>
+      <c r="K76" s="9"/>
       <c r="L76" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M76" s="9" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="Q76" s="37">
-        <v>1500</v>
-      </c>
-      <c r="V76" t="s">
-        <v>254</v>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="U76" s="5"/>
       <c r="Y76">
         <f>COUNTIFS(J:J,"in",L:L,AB76,H:H,"&gt;0")</f>
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="AB76" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="AC76">
         <v>0</v>
@@ -9682,30 +9674,32 @@
     </row>
     <row r="77" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B77" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C77" s="9" t="s">
-        <v>90</v>
+        <v>13</v>
       </c>
       <c r="D77" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="E77" s="10"/>
+      <c r="E77" s="10">
+        <v>46211</v>
+      </c>
       <c r="F77" s="10">
-        <v>46211</v>
+        <v>46214</v>
       </c>
       <c r="G77" s="9" t="s">
         <v>20</v>
       </c>
       <c r="H77" s="9"/>
       <c r="I77" s="10">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="J77" s="9" t="s">
         <v>16</v>
       </c>
       <c r="K77" s="9" t="s">
-        <v>417</v>
+        <v>432</v>
       </c>
       <c r="L77" s="9" t="s">
         <v>17</v>
@@ -9722,7 +9716,7 @@
     </row>
     <row r="78" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B78" s="9" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C78" s="9" t="s">
         <v>90</v>
@@ -9732,20 +9726,22 @@
       </c>
       <c r="E78" s="10"/>
       <c r="F78" s="10">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="G78" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H78" s="9"/>
+        <v>99</v>
+      </c>
+      <c r="H78" s="9">
+        <v>2</v>
+      </c>
       <c r="I78" s="10">
-        <v>46215</v>
+        <v>46216</v>
       </c>
       <c r="J78" s="9" t="s">
         <v>16</v>
       </c>
       <c r="K78" s="9" t="s">
-        <v>437</v>
+        <v>196</v>
       </c>
       <c r="L78" s="9" t="s">
         <v>17</v>
@@ -9757,76 +9753,88 @@
         <v>2000</v>
       </c>
       <c r="V78" t="s">
-        <v>435</v>
-      </c>
-      <c r="W78" t="s">
-        <v>436</v>
+        <v>196</v>
+      </c>
+      <c r="Y78">
+        <f>COUNTIFS(J:J,"in",L:L,AB78)</f>
+        <v>11</v>
+      </c>
+      <c r="AB78" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="79" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B79" s="9" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C79" s="9" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E79" s="10"/>
+        <v>28</v>
+      </c>
+      <c r="E79" s="10">
+        <v>46209</v>
+      </c>
       <c r="F79" s="10">
-        <v>46573</v>
+        <v>46210</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>24</v>
+        <v>110</v>
       </c>
       <c r="H79" s="9"/>
       <c r="I79" s="10">
-        <v>46221</v>
+        <v>46215</v>
       </c>
       <c r="J79" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K79" s="9"/>
+      <c r="K79" s="9" t="s">
+        <v>109</v>
+      </c>
       <c r="L79" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M79" s="9" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="Q79" s="37">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="V79" t="s">
-        <v>435</v>
-      </c>
-      <c r="W79" t="s">
-        <v>440</v>
+        <v>254</v>
+      </c>
+      <c r="Y79">
+        <f>COUNTIFS(J:J,"in",L:L,AB79,H:H,"&gt;0")</f>
+        <v>4</v>
       </c>
       <c r="AB79" t="s">
-        <v>17</v>
+        <v>48</v>
+      </c>
+      <c r="AC79">
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B80" s="9" t="s">
-        <v>433</v>
+        <v>115</v>
       </c>
       <c r="C80" s="9" t="s">
-        <v>127</v>
+        <v>90</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="E80" s="10"/>
       <c r="F80" s="10">
-        <v>46217</v>
+        <v>46211</v>
       </c>
       <c r="G80" s="9" t="s">
         <v>20</v>
       </c>
       <c r="H80" s="9"/>
       <c r="I80" s="10">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="J80" s="9" t="s">
         <v>16</v>
@@ -9835,7 +9843,7 @@
         <v>417</v>
       </c>
       <c r="L80" s="9" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="M80" s="9" t="s">
         <v>42</v>
@@ -9847,9 +9855,9 @@
         <v>254</v>
       </c>
     </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B81" s="9" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="C81" s="9" t="s">
         <v>90</v>
@@ -9857,63 +9865,59 @@
       <c r="D81" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E81" s="10">
-        <v>46202</v>
-      </c>
+      <c r="E81" s="10"/>
       <c r="F81" s="10">
         <v>46206</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>96</v>
+        <v>24</v>
       </c>
       <c r="H81" s="9"/>
       <c r="I81" s="10">
-        <v>46219</v>
+        <v>46215</v>
       </c>
       <c r="J81" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K81" s="9"/>
+      <c r="K81" s="9" t="s">
+        <v>437</v>
+      </c>
       <c r="L81" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M81" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="P81" t="s">
-        <v>527</v>
-      </c>
       <c r="Q81" s="37">
         <v>2000</v>
       </c>
+      <c r="V81" t="s">
+        <v>435</v>
+      </c>
       <c r="W81" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="82" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B82" s="9" t="s">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c r="C82" s="9" t="s">
-        <v>22</v>
+        <v>112</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="E82" s="10">
-        <v>46212</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="E82" s="10"/>
       <c r="F82" s="10">
-        <v>46217</v>
+        <v>46573</v>
       </c>
       <c r="G82" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="H82" s="9">
-        <v>4</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="H82" s="9"/>
       <c r="I82" s="10">
-        <v>46223</v>
+        <v>46221</v>
       </c>
       <c r="J82" s="9" t="s">
         <v>16</v>
@@ -9925,9 +9929,6 @@
       <c r="M82" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="P82" t="s">
-        <v>181</v>
-      </c>
       <c r="Q82" s="37">
         <v>2000</v>
       </c>
@@ -9935,47 +9936,45 @@
         <v>435</v>
       </c>
       <c r="W82" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
+        <v>440</v>
+      </c>
+      <c r="AB82" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B83" s="9" t="s">
-        <v>172</v>
+        <v>433</v>
       </c>
       <c r="C83" s="9" t="s">
-        <v>173</v>
+        <v>127</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E83" s="10">
-        <v>46216</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="E83" s="10"/>
       <c r="F83" s="10">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H83" s="9"/>
       <c r="I83" s="10">
-        <v>46225</v>
+        <v>46219</v>
       </c>
       <c r="J83" s="9" t="s">
         <v>16</v>
       </c>
       <c r="K83" s="9" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
       <c r="L83" s="9" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="M83" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="P83" t="s">
-        <v>181</v>
-      </c>
       <c r="Q83" s="37">
         <v>2000</v>
       </c>
@@ -9983,37 +9982,33 @@
         <v>254</v>
       </c>
     </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B84" s="9" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C84" s="9" t="s">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="E84" s="10">
-        <v>46215</v>
+        <v>46202</v>
       </c>
       <c r="F84" s="10">
-        <v>46216</v>
+        <v>46206</v>
       </c>
       <c r="G84" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H84" s="9">
-        <v>2</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="H84" s="9"/>
       <c r="I84" s="10">
-        <v>46225</v>
+        <v>46219</v>
       </c>
       <c r="J84" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K84" s="9" t="s">
-        <v>47</v>
-      </c>
+      <c r="K84" s="9"/>
       <c r="L84" s="9" t="s">
         <v>17</v>
       </c>
@@ -10021,42 +10016,39 @@
         <v>42</v>
       </c>
       <c r="P84" t="s">
-        <v>181</v>
+        <v>526</v>
       </c>
       <c r="Q84" s="37">
         <v>2000</v>
       </c>
-      <c r="V84" t="s">
-        <v>435</v>
-      </c>
       <c r="W84" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="85" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B85" s="9" t="s">
-        <v>198</v>
+        <v>27</v>
       </c>
       <c r="C85" s="9" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="E85" s="10">
-        <v>46162</v>
+        <v>46212</v>
       </c>
       <c r="F85" s="10">
-        <v>46218</v>
+        <v>46217</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>88</v>
+        <v>165</v>
       </c>
       <c r="H85" s="9">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="I85" s="10">
-        <v>46227</v>
+        <v>46223</v>
       </c>
       <c r="J85" s="9" t="s">
         <v>16</v>
@@ -10066,7 +10058,7 @@
         <v>17</v>
       </c>
       <c r="M85" s="9" t="s">
-        <v>413</v>
+        <v>42</v>
       </c>
       <c r="P85" t="s">
         <v>181</v>
@@ -10074,13 +10066,6 @@
       <c r="Q85" s="37">
         <v>2000</v>
       </c>
-      <c r="R85" t="s">
-        <v>128</v>
-      </c>
-      <c r="T85" t="s">
-        <v>130</v>
-      </c>
-      <c r="U85" s="5"/>
       <c r="V85" t="s">
         <v>435</v>
       </c>
@@ -10088,35 +10073,35 @@
         <v>47</v>
       </c>
     </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B86" s="9" t="s">
-        <v>132</v>
+        <v>172</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>13</v>
+        <v>173</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="E86" s="10">
-        <v>46200</v>
+        <v>46216</v>
       </c>
       <c r="F86" s="10">
-        <v>46204</v>
+        <v>46218</v>
       </c>
       <c r="G86" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H86" s="9">
-        <v>3</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="H86" s="9"/>
       <c r="I86" s="10">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="J86" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K86" s="9"/>
+      <c r="K86" s="9" t="s">
+        <v>432</v>
+      </c>
       <c r="L86" s="9" t="s">
         <v>17</v>
       </c>
@@ -10129,41 +10114,41 @@
       <c r="Q86" s="37">
         <v>2000</v>
       </c>
-      <c r="U86" s="5"/>
       <c r="V86" t="s">
-        <v>435</v>
-      </c>
-      <c r="W86" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="87" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B87" s="9" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C87" s="9" t="s">
-        <v>90</v>
+        <v>33</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E87" s="10"/>
+        <v>40</v>
+      </c>
+      <c r="E87" s="10">
+        <v>46215</v>
+      </c>
       <c r="F87" s="10">
-        <v>46206</v>
+        <v>46216</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="H87" s="9">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I87" s="10">
-        <v>46218</v>
+        <v>46225</v>
       </c>
       <c r="J87" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K87" s="9"/>
+      <c r="K87" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="L87" s="9" t="s">
         <v>17</v>
       </c>
@@ -10176,29 +10161,35 @@
       <c r="Q87" s="37">
         <v>2000</v>
       </c>
-      <c r="U87" s="5"/>
+      <c r="V87" t="s">
+        <v>435</v>
+      </c>
       <c r="W87" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="88" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B88" s="9" t="s">
-        <v>21</v>
+        <v>198</v>
       </c>
       <c r="C88" s="9" t="s">
-        <v>323</v>
+        <v>90</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E88" s="10"/>
+        <v>174</v>
+      </c>
+      <c r="E88" s="10">
+        <v>46162</v>
+      </c>
       <c r="F88" s="10">
-        <v>46222</v>
+        <v>46218</v>
       </c>
       <c r="G88" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H88" s="9"/>
+        <v>88</v>
+      </c>
+      <c r="H88" s="9">
+        <v>12</v>
+      </c>
       <c r="I88" s="10">
         <v>46227</v>
       </c>
@@ -10207,19 +10198,22 @@
       </c>
       <c r="K88" s="9"/>
       <c r="L88" s="9" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="M88" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="O88" t="s">
-        <v>341</v>
+        <v>413</v>
       </c>
       <c r="P88" t="s">
         <v>181</v>
       </c>
       <c r="Q88" s="37">
         <v>2000</v>
+      </c>
+      <c r="R88" t="s">
+        <v>128</v>
+      </c>
+      <c r="T88" t="s">
+        <v>130</v>
       </c>
       <c r="U88" s="5"/>
       <c r="V88" t="s">
@@ -10229,27 +10223,27 @@
         <v>47</v>
       </c>
     </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B89" s="9" t="s">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="C89" s="9" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="E89" s="10">
+        <v>46200</v>
+      </c>
+      <c r="F89" s="10">
         <v>46204</v>
       </c>
-      <c r="F89" s="10">
-        <v>46206</v>
-      </c>
       <c r="G89" s="9" t="s">
-        <v>88</v>
+        <v>20</v>
       </c>
       <c r="H89" s="9">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I89" s="10">
         <v>46223</v>
@@ -10257,18 +10251,13 @@
       <c r="J89" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K89" s="9" t="s">
-        <v>47</v>
-      </c>
+      <c r="K89" s="9"/>
       <c r="L89" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M89" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="N89" t="s">
-        <v>448</v>
-      </c>
       <c r="P89" t="s">
         <v>181</v>
       </c>
@@ -10276,34 +10265,35 @@
         <v>2000</v>
       </c>
       <c r="U89" s="5"/>
+      <c r="V89" t="s">
+        <v>435</v>
+      </c>
       <c r="W89" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="90" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B90" s="9" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="C90" s="9" t="s">
         <v>90</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E90" s="10">
-        <v>46204</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="E90" s="10"/>
       <c r="F90" s="10">
-        <v>46215</v>
+        <v>46206</v>
       </c>
       <c r="G90" s="9" t="s">
-        <v>20</v>
+        <v>99</v>
       </c>
       <c r="H90" s="9">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="I90" s="10">
-        <v>46232</v>
+        <v>46218</v>
       </c>
       <c r="J90" s="9" t="s">
         <v>16</v>
@@ -10322,40 +10312,44 @@
         <v>2000</v>
       </c>
       <c r="U90" s="5"/>
-    </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W90" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="91" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B91" s="9" t="s">
-        <v>124</v>
+        <v>21</v>
       </c>
       <c r="C91" s="9" t="s">
-        <v>90</v>
+        <v>323</v>
       </c>
       <c r="D91" s="9" t="s">
         <v>23</v>
       </c>
       <c r="E91" s="10"/>
       <c r="F91" s="10">
-        <v>46224</v>
+        <v>46222</v>
       </c>
       <c r="G91" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H91" s="9">
-        <v>15</v>
-      </c>
+      <c r="H91" s="9"/>
       <c r="I91" s="10">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="J91" s="9" t="s">
         <v>16</v>
       </c>
       <c r="K91" s="9"/>
       <c r="L91" s="9" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="M91" s="9" t="s">
         <v>42</v>
       </c>
+      <c r="O91" t="s">
+        <v>341</v>
+      </c>
       <c r="P91" t="s">
         <v>181</v>
       </c>
@@ -10363,11 +10357,14 @@
         <v>2000</v>
       </c>
       <c r="U91" s="5"/>
+      <c r="V91" t="s">
+        <v>435</v>
+      </c>
       <c r="W91" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="92" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B92" s="9" t="s">
         <v>86</v>
       </c>
@@ -10390,7 +10387,7 @@
         <v>20</v>
       </c>
       <c r="I92" s="10">
-        <v>46210</v>
+        <v>46223</v>
       </c>
       <c r="J92" s="9" t="s">
         <v>16</v>
@@ -10404,6 +10401,9 @@
       <c r="M92" s="9" t="s">
         <v>42</v>
       </c>
+      <c r="N92" t="s">
+        <v>448</v>
+      </c>
       <c r="P92" t="s">
         <v>181</v>
       </c>
@@ -10411,41 +10411,44 @@
         <v>2000</v>
       </c>
       <c r="U92" s="5"/>
-    </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W92" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="93" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B93" s="9" t="s">
-        <v>175</v>
+        <v>118</v>
       </c>
       <c r="C93" s="9" t="s">
-        <v>176</v>
+        <v>90</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="E93" s="10">
-        <v>46153</v>
+        <v>46204</v>
       </c>
       <c r="F93" s="10">
-        <v>46218</v>
+        <v>46215</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H93" s="9"/>
+        <v>20</v>
+      </c>
+      <c r="H93" s="9">
+        <v>15</v>
+      </c>
       <c r="I93" s="10">
-        <v>46234</v>
+        <v>46232</v>
       </c>
       <c r="J93" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K93" s="9" t="s">
-        <v>47</v>
-      </c>
+      <c r="K93" s="9"/>
       <c r="L93" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M93" s="9" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="P93" t="s">
         <v>181</v>
@@ -10455,47 +10458,39 @@
       </c>
       <c r="U93" s="5"/>
     </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>131</v>
-      </c>
+    <row r="94" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B94" s="9" t="s">
-        <v>187</v>
+        <v>124</v>
       </c>
       <c r="C94" s="9" t="s">
-        <v>188</v>
+        <v>90</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="E94" s="10">
-        <v>46214</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="E94" s="10"/>
       <c r="F94" s="10">
-        <v>46230</v>
+        <v>46224</v>
       </c>
       <c r="G94" s="9" t="s">
-        <v>434</v>
-      </c>
-      <c r="H94" s="9"/>
+        <v>24</v>
+      </c>
+      <c r="H94" s="9">
+        <v>15</v>
+      </c>
       <c r="I94" s="10">
-        <v>46235</v>
+        <v>46224</v>
       </c>
       <c r="J94" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K94" s="9" t="s">
-        <v>47</v>
-      </c>
+      <c r="K94" s="9"/>
       <c r="L94" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M94" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="N94" t="s">
-        <v>427</v>
-      </c>
       <c r="P94" t="s">
         <v>181</v>
       </c>
@@ -10503,79 +10498,83 @@
         <v>2000</v>
       </c>
       <c r="U94" s="5"/>
-    </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W94" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="95" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B95" s="9" t="s">
-        <v>332</v>
+        <v>86</v>
       </c>
       <c r="C95" s="9" t="s">
-        <v>58</v>
+        <v>33</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="E95" s="10">
-        <v>46229</v>
+        <v>46204</v>
       </c>
       <c r="F95" s="10">
-        <v>46231</v>
+        <v>46206</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H95" s="9"/>
+        <v>88</v>
+      </c>
+      <c r="H95" s="9">
+        <v>20</v>
+      </c>
       <c r="I95" s="10">
-        <v>46235</v>
+        <v>46210</v>
       </c>
       <c r="J95" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K95" s="9"/>
+      <c r="K95" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="L95" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M95" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="N95" t="s">
-        <v>441</v>
+        <v>42</v>
       </c>
       <c r="P95" t="s">
         <v>181</v>
       </c>
       <c r="Q95" s="37">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="U95" s="5"/>
     </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:28" x14ac:dyDescent="0.25">
       <c r="B96" s="9" t="s">
-        <v>443</v>
+        <v>175</v>
       </c>
       <c r="C96" s="9" t="s">
-        <v>444</v>
+        <v>176</v>
       </c>
       <c r="D96" s="9" t="s">
         <v>23</v>
       </c>
       <c r="E96" s="10">
-        <v>46206</v>
+        <v>46153</v>
       </c>
       <c r="F96" s="10">
-        <v>46232</v>
+        <v>46218</v>
       </c>
       <c r="G96" s="9" t="s">
-        <v>99</v>
+        <v>24</v>
       </c>
       <c r="H96" s="9"/>
       <c r="I96" s="10">
-        <v>46237</v>
+        <v>46234</v>
       </c>
       <c r="J96" s="9" t="s">
         <v>16</v>
       </c>
       <c r="K96" s="9" t="s">
-        <v>390</v>
+        <v>47</v>
       </c>
       <c r="L96" s="9" t="s">
         <v>17</v>
@@ -10583,41 +10582,46 @@
       <c r="M96" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="P96" s="9" t="s">
+      <c r="P96" t="s">
         <v>181</v>
       </c>
       <c r="Q96" s="37">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="U96" s="5"/>
     </row>
-    <row r="97" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>131</v>
+      </c>
       <c r="B97" s="9" t="s">
-        <v>337</v>
+        <v>187</v>
       </c>
       <c r="C97" s="9" t="s">
-        <v>414</v>
+        <v>188</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>23</v>
+        <v>166</v>
       </c>
       <c r="E97" s="10">
-        <v>46227</v>
+        <v>46214</v>
       </c>
       <c r="F97" s="10">
         <v>46230</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>24</v>
+        <v>434</v>
       </c>
       <c r="H97" s="9"/>
       <c r="I97" s="10">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="J97" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K97" s="9"/>
+      <c r="K97" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="L97" s="9" t="s">
         <v>17</v>
       </c>
@@ -10633,32 +10637,30 @@
       <c r="Q97" s="37">
         <v>2000</v>
       </c>
-      <c r="R97" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="98" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="U97" s="5"/>
+    </row>
+    <row r="98" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B98" s="9" t="s">
-        <v>100</v>
+        <v>332</v>
       </c>
       <c r="C98" s="9" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="E98" s="10">
-        <v>46230</v>
+        <v>46229</v>
       </c>
       <c r="F98" s="10">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="G98" s="9" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="H98" s="9"/>
       <c r="I98" s="10">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="J98" s="9" t="s">
         <v>16</v>
@@ -10668,126 +10670,130 @@
         <v>17</v>
       </c>
       <c r="M98" s="9" t="s">
-        <v>42</v>
+        <v>55</v>
+      </c>
+      <c r="N98" t="s">
+        <v>441</v>
       </c>
       <c r="P98" t="s">
         <v>181</v>
       </c>
       <c r="Q98" s="37">
-        <v>2000</v>
-      </c>
-      <c r="U98" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="99" spans="2:24" x14ac:dyDescent="0.25">
+        <v>1000</v>
+      </c>
+      <c r="U98" s="5"/>
+    </row>
+    <row r="99" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B99" s="9" t="s">
-        <v>77</v>
+        <v>443</v>
       </c>
       <c r="C99" s="9" t="s">
-        <v>90</v>
+        <v>444</v>
       </c>
       <c r="D99" s="9" t="s">
         <v>23</v>
       </c>
       <c r="E99" s="10">
-        <v>46215</v>
+        <v>46206</v>
       </c>
       <c r="F99" s="10">
-        <v>46226</v>
+        <v>46232</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H99" s="9">
-        <v>11</v>
-      </c>
+        <v>99</v>
+      </c>
+      <c r="H99" s="9"/>
       <c r="I99" s="10">
         <v>46237</v>
       </c>
       <c r="J99" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K99" s="9"/>
+      <c r="K99" s="9" t="s">
+        <v>390</v>
+      </c>
       <c r="L99" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M99" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="P99" t="s">
+        <v>55</v>
+      </c>
+      <c r="P99" s="9" t="s">
         <v>181</v>
       </c>
       <c r="Q99" s="37">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="U99" s="5"/>
     </row>
-    <row r="100" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B100" s="9" t="s">
-        <v>78</v>
+        <v>337</v>
       </c>
       <c r="C100" s="9" t="s">
-        <v>33</v>
+        <v>414</v>
       </c>
       <c r="D100" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E100" s="10"/>
+      <c r="E100" s="10">
+        <v>46227</v>
+      </c>
       <c r="F100" s="10">
-        <v>46212</v>
+        <v>46230</v>
       </c>
       <c r="G100" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H100" s="9">
-        <v>16</v>
-      </c>
+      <c r="H100" s="9"/>
       <c r="I100" s="10">
-        <v>46217</v>
+        <v>46234</v>
       </c>
       <c r="J100" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K100" s="9" t="s">
-        <v>47</v>
-      </c>
+      <c r="K100" s="9"/>
       <c r="L100" s="9" t="s">
         <v>17</v>
       </c>
       <c r="M100" s="9" t="s">
         <v>42</v>
       </c>
+      <c r="N100" t="s">
+        <v>427</v>
+      </c>
       <c r="P100" t="s">
         <v>181</v>
       </c>
       <c r="Q100" s="37">
         <v>2000</v>
       </c>
-      <c r="U100" s="5"/>
-    </row>
-    <row r="101" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="R100" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="101" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B101" s="9" t="s">
-        <v>425</v>
+        <v>100</v>
       </c>
       <c r="C101" s="9" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>426</v>
+        <v>44</v>
       </c>
       <c r="E101" s="10">
-        <v>46228</v>
+        <v>46230</v>
       </c>
       <c r="F101" s="10">
-        <v>46233</v>
+        <v>46232</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="H101" s="9"/>
       <c r="I101" s="10">
-        <v>46239</v>
+        <v>46234</v>
       </c>
       <c r="J101" s="9" t="s">
         <v>16</v>
@@ -10799,44 +10805,47 @@
       <c r="M101" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="N101" t="s">
-        <v>449</v>
-      </c>
       <c r="P101" t="s">
         <v>181</v>
       </c>
       <c r="Q101" s="37">
         <v>2000</v>
       </c>
-      <c r="U101" s="5"/>
-    </row>
-    <row r="102" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="U101" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="102" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B102" s="9" t="s">
-        <v>340</v>
+        <v>77</v>
       </c>
       <c r="C102" s="9" t="s">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E102" s="10"/>
+        <v>23</v>
+      </c>
+      <c r="E102" s="10">
+        <v>46215</v>
+      </c>
       <c r="F102" s="10">
-        <v>46240</v>
+        <v>46226</v>
       </c>
       <c r="G102" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H102" s="9"/>
+        <v>24</v>
+      </c>
+      <c r="H102" s="9">
+        <v>11</v>
+      </c>
       <c r="I102" s="10">
-        <v>46240</v>
+        <v>46237</v>
       </c>
       <c r="J102" s="9" t="s">
         <v>16</v>
       </c>
       <c r="K102" s="9"/>
       <c r="L102" s="9" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="M102" s="9" t="s">
         <v>42</v>
@@ -10849,33 +10858,35 @@
       </c>
       <c r="U102" s="5"/>
     </row>
-    <row r="103" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B103" s="9" t="s">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="C103" s="9" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="D103" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E103" s="10">
-        <v>46231</v>
-      </c>
+      <c r="E103" s="10"/>
       <c r="F103" s="10">
-        <v>46236</v>
+        <v>46212</v>
       </c>
       <c r="G103" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H103" s="9"/>
+      <c r="H103" s="9">
+        <v>16</v>
+      </c>
       <c r="I103" s="10">
-        <v>46209</v>
+        <v>46217</v>
       </c>
       <c r="J103" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="K103" s="9"/>
+      <c r="K103" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="L103" s="9" t="s">
         <v>17</v>
       </c>
@@ -10890,28 +10901,28 @@
       </c>
       <c r="U103" s="5"/>
     </row>
-    <row r="104" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B104" s="9" t="s">
-        <v>116</v>
+        <v>425</v>
       </c>
       <c r="C104" s="9" t="s">
-        <v>90</v>
+        <v>22</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E104" s="10"/>
+        <v>426</v>
+      </c>
+      <c r="E104" s="10">
+        <v>46228</v>
+      </c>
       <c r="F104" s="10">
-        <v>46211</v>
+        <v>46233</v>
       </c>
       <c r="G104" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H104" s="9">
-        <v>25</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="H104" s="9"/>
       <c r="I104" s="10">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="J104" s="9" t="s">
         <v>16</v>
@@ -10923,6 +10934,9 @@
       <c r="M104" s="9" t="s">
         <v>42</v>
       </c>
+      <c r="N104" t="s">
+        <v>449</v>
+      </c>
       <c r="P104" t="s">
         <v>181</v>
       </c>
@@ -10931,33 +10945,33 @@
       </c>
       <c r="U104" s="5"/>
     </row>
-    <row r="105" spans="2:24" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B105" s="9" t="s">
-        <v>21</v>
+        <v>340</v>
       </c>
       <c r="C105" s="9" t="s">
-        <v>323</v>
+        <v>13</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="E105" s="10"/>
       <c r="F105" s="10">
-        <v>46236</v>
+        <v>46240</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="H105" s="9"/>
       <c r="I105" s="10">
-        <v>46244</v>
+        <v>46240</v>
       </c>
       <c r="J105" s="9" t="s">
         <v>16</v>
       </c>
       <c r="K105" s="9"/>
       <c r="L105" s="9" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="M105" s="9" t="s">
         <v>42</v>
@@ -10968,23 +10982,30 @@
       <c r="Q105" s="37">
         <v>2000</v>
       </c>
-    </row>
-    <row r="106" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="U105" s="5"/>
+    </row>
+    <row r="106" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B106" s="9" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C106" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D106" s="9"/>
-      <c r="E106" s="10"/>
-      <c r="F106" s="10"/>
-      <c r="G106" s="9"/>
-      <c r="H106" s="9">
-        <v>30</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E106" s="10">
+        <v>46231</v>
+      </c>
+      <c r="F106" s="10">
+        <v>46236</v>
+      </c>
+      <c r="G106" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H106" s="9"/>
       <c r="I106" s="10">
-        <v>46241</v>
+        <v>46209</v>
       </c>
       <c r="J106" s="9" t="s">
         <v>16</v>
@@ -10994,45 +11015,38 @@
         <v>17</v>
       </c>
       <c r="M106" s="9" t="s">
-        <v>35</v>
-      </c>
-      <c r="O106" s="20"/>
-      <c r="P106" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="P106" t="s">
         <v>181</v>
       </c>
       <c r="Q106" s="37">
-        <v>800</v>
-      </c>
-      <c r="R106" t="s">
-        <v>37</v>
+        <v>2000</v>
       </c>
       <c r="U106" s="5"/>
-      <c r="X106" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="107" spans="2:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B107" s="9" t="s">
-        <v>185</v>
+        <v>116</v>
       </c>
       <c r="C107" s="9" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="E107" s="10"/>
       <c r="F107" s="10">
-        <v>46188</v>
+        <v>46211</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>66</v>
+        <v>24</v>
       </c>
       <c r="H107" s="9">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="I107" s="10">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="J107" s="9" t="s">
         <v>16</v>
@@ -11050,31 +11064,28 @@
       <c r="Q107" s="37">
         <v>2000</v>
       </c>
-    </row>
-    <row r="108" spans="2:24" x14ac:dyDescent="0.25">
+      <c r="U107" s="5"/>
+    </row>
+    <row r="108" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B108" s="9" t="s">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="C108" s="9" t="s">
-        <v>80</v>
+        <v>323</v>
       </c>
       <c r="D108" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="E108" s="10">
-        <v>46206</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="E108" s="10"/>
       <c r="F108" s="10">
-        <v>46207</v>
+        <v>46236</v>
       </c>
       <c r="G108" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="H108" s="9">
-        <v>5</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="H108" s="9"/>
       <c r="I108" s="10">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="J108" s="9" t="s">
         <v>16</v>
@@ -11092,32 +11103,23 @@
       <c r="Q108" s="37">
         <v>2000</v>
       </c>
-      <c r="R108" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="109" spans="2:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="109" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B109" s="9" t="s">
-        <v>63</v>
+        <v>32</v>
       </c>
       <c r="C109" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D109" s="9" t="s">
-        <v>65</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="D109" s="9"/>
       <c r="E109" s="10"/>
-      <c r="F109" s="10">
-        <v>46203</v>
-      </c>
-      <c r="G109" s="9" t="s">
-        <v>66</v>
-      </c>
+      <c r="F109" s="10"/>
+      <c r="G109" s="9"/>
       <c r="H109" s="9">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="I109" s="10">
-        <v>46231</v>
+        <v>46241</v>
       </c>
       <c r="J109" s="9" t="s">
         <v>16</v>
@@ -11127,39 +11129,45 @@
         <v>17</v>
       </c>
       <c r="M109" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="P109" t="s">
+        <v>35</v>
+      </c>
+      <c r="O109" s="20"/>
+      <c r="P109" s="20" t="s">
         <v>181</v>
       </c>
       <c r="Q109" s="37">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="110" spans="2:24" x14ac:dyDescent="0.25">
+        <v>800</v>
+      </c>
+      <c r="R109" t="s">
+        <v>37</v>
+      </c>
+      <c r="U109" s="5"/>
+      <c r="X109" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="110" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B110" s="9" t="s">
-        <v>342</v>
+        <v>185</v>
       </c>
       <c r="C110" s="9" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="D110" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E110" s="10">
-        <v>46206</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="E110" s="10"/>
       <c r="F110" s="10">
-        <v>46221</v>
+        <v>46188</v>
       </c>
       <c r="G110" s="9" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="H110" s="9">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="I110" s="10">
-        <v>46244</v>
+        <v>46242</v>
       </c>
       <c r="J110" s="9" t="s">
         <v>16</v>
@@ -11171,41 +11179,37 @@
       <c r="M110" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="O110" t="s">
-        <v>341</v>
-      </c>
       <c r="P110" t="s">
         <v>181</v>
       </c>
       <c r="Q110" s="37">
         <v>2000</v>
       </c>
-      <c r="T110" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="111" spans="2:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B111" s="9" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
       <c r="C111" s="9" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="D111" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E111" s="10"/>
+        <v>81</v>
+      </c>
+      <c r="E111" s="10">
+        <v>46206</v>
+      </c>
       <c r="F111" s="10">
-        <v>46203</v>
+        <v>46207</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="H111" s="9">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="I111" s="10">
-        <v>46238</v>
+        <v>46237</v>
       </c>
       <c r="J111" s="9" t="s">
         <v>16</v>
@@ -11215,1207 +11219,1442 @@
         <v>17</v>
       </c>
       <c r="M111" s="9" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="P111" t="s">
         <v>181</v>
       </c>
       <c r="Q111" s="37">
+        <v>2000</v>
+      </c>
+      <c r="R111" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="112" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="B112" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C112" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D112" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E112" s="10"/>
+      <c r="F112" s="10">
+        <v>46203</v>
+      </c>
+      <c r="G112" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H112" s="9">
+        <v>60</v>
+      </c>
+      <c r="I112" s="10">
+        <v>46231</v>
+      </c>
+      <c r="J112" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K112" s="9"/>
+      <c r="L112" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M112" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="P112" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q112" s="37">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="113" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="B113" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="C113" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="D113" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E113" s="10">
+        <v>46206</v>
+      </c>
+      <c r="F113" s="10">
+        <v>46221</v>
+      </c>
+      <c r="G113" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H113" s="9">
+        <v>3</v>
+      </c>
+      <c r="I113" s="10">
+        <v>46244</v>
+      </c>
+      <c r="J113" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K113" s="9"/>
+      <c r="L113" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M113" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="O113" t="s">
+        <v>341</v>
+      </c>
+      <c r="P113" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q113" s="37">
+        <v>2000</v>
+      </c>
+      <c r="T113" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="114" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="B114" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C114" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D114" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="E114" s="10"/>
+      <c r="F114" s="10">
+        <v>46203</v>
+      </c>
+      <c r="G114" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="H114" s="9">
+        <v>60</v>
+      </c>
+      <c r="I114" s="10">
+        <v>46238</v>
+      </c>
+      <c r="J114" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K114" s="9"/>
+      <c r="L114" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M114" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="P114" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q114" s="37">
         <v>1000</v>
       </c>
     </row>
-    <row r="112" spans="2:24" x14ac:dyDescent="0.25">
-      <c r="B112" s="6" t="s">
+    <row r="115" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="B115" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="C112" s="6"/>
-      <c r="D112" s="6"/>
-      <c r="E112" s="7">
+      <c r="C115" s="6"/>
+      <c r="D115" s="6"/>
+      <c r="E115" s="7">
         <v>46234</v>
       </c>
-      <c r="F112" s="7"/>
-      <c r="G112" s="6" t="s">
+      <c r="F115" s="7"/>
+      <c r="G115" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="H112" s="6">
+      <c r="H115" s="6">
         <v>9</v>
       </c>
-      <c r="I112" s="6"/>
-      <c r="J112" s="6" t="s">
+      <c r="I115" s="6"/>
+      <c r="J115" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="K112" s="6"/>
-      <c r="L112" s="6" t="s">
+      <c r="K115" s="6"/>
+      <c r="L115" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="M112" s="6" t="s">
+      <c r="M115" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="T112" t="s">
+      <c r="T115" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="116" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="B116" s="9" t="s">
+        <v>100</v>
+      </c>
+      <c r="C116" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D116" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="E116" s="10">
+        <v>46240</v>
+      </c>
+      <c r="F116" s="10">
+        <v>46241</v>
+      </c>
+      <c r="G116" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H116" s="9"/>
+      <c r="I116" s="10">
+        <v>46242</v>
+      </c>
+      <c r="J116" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K116" s="9"/>
+      <c r="L116" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M116" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="P116" t="s">
+        <v>181</v>
+      </c>
+      <c r="Q116" s="37">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="117" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="B117" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="C117" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="D117" s="9" t="s">
+        <v>504</v>
+      </c>
+      <c r="E117" s="10">
+        <v>46237</v>
+      </c>
+      <c r="F117" s="10">
+        <v>46241</v>
+      </c>
+      <c r="G117" s="9" t="s">
         <v>528</v>
       </c>
-    </row>
-    <row r="113" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="I113" s="2"/>
-    </row>
-    <row r="114" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="AF114" s="39"/>
-    </row>
-    <row r="116" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="X116" s="2">
-        <f ca="1">+TODAY()</f>
-        <v>46245</v>
-      </c>
-      <c r="Y116" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="117" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A117" t="s">
-        <v>182</v>
-      </c>
-      <c r="B117" t="s">
-        <v>184</v>
+      <c r="H117" s="9"/>
+      <c r="I117" s="10">
+        <v>46244</v>
+      </c>
+      <c r="J117" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="K117" s="9"/>
+      <c r="L117" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="M117" s="9" t="s">
+        <v>42</v>
       </c>
       <c r="P117" t="s">
         <v>181</v>
       </c>
-      <c r="X117" s="1" t="s">
+      <c r="Q117" s="37">
+        <v>2000</v>
+      </c>
+      <c r="S117" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="118" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AF118" s="39"/>
+    </row>
+    <row r="120" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="X120" s="2">
+        <f ca="1">+TODAY()</f>
+        <v>46251</v>
+      </c>
+      <c r="Y120" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="121" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>182</v>
+      </c>
+      <c r="B121" t="s">
+        <v>184</v>
+      </c>
+      <c r="P121" t="s">
+        <v>181</v>
+      </c>
+      <c r="X121" s="1" t="s">
         <v>329</v>
       </c>
-      <c r="Y117" s="1">
+      <c r="Y121" s="1">
         <f>COUNTIFS(J:J,"in")</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="118" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A118" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="122" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
         <v>182</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B122" t="s">
         <v>183</v>
       </c>
-      <c r="P118" t="s">
+      <c r="P122" t="s">
         <v>181</v>
       </c>
-      <c r="X118" s="30" t="s">
+      <c r="X122" s="30" t="s">
         <v>325</v>
       </c>
-      <c r="Y118" s="31">
-        <f>COUNTIFS(J:J,"in",L:L,AB79)</f>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="119" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="X119" s="30"/>
-      <c r="Y119" s="31"/>
-    </row>
-    <row r="120" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="B120" s="6" t="s">
+      <c r="Y122" s="31">
+        <f>COUNTIFS(J:J,"in",L:L,AB82)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="X123" s="30"/>
+      <c r="Y123" s="31"/>
+    </row>
+    <row r="124" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="B124" s="6" t="s">
         <v>468</v>
       </c>
-      <c r="C120" s="6"/>
-      <c r="D120" s="6"/>
-      <c r="E120" s="7">
+      <c r="C124" s="6"/>
+      <c r="D124" s="6"/>
+      <c r="E124" s="7">
         <v>46232</v>
       </c>
-      <c r="F120" s="7"/>
-      <c r="G120" s="6" t="s">
+      <c r="F124" s="7"/>
+      <c r="G124" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="H120" s="6"/>
-      <c r="I120" s="6"/>
-      <c r="J120" s="6"/>
-      <c r="K120" s="6"/>
-      <c r="L120" s="6"/>
-      <c r="M120" s="6"/>
-      <c r="X120" s="32" t="s">
+      <c r="H124" s="6"/>
+      <c r="I124" s="6"/>
+      <c r="J124" s="6"/>
+      <c r="K124" s="6"/>
+      <c r="L124" s="6"/>
+      <c r="M124" s="6"/>
+      <c r="X124" s="32" t="s">
         <v>324</v>
-      </c>
-      <c r="Y120" s="20">
-        <f>COUNTIFS(J:J,"in",L:L,AB73,H:H,"&gt;0")</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="121" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="B121" s="6" t="s">
-        <v>471</v>
-      </c>
-      <c r="C121" s="6"/>
-      <c r="D121" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="E121" s="7">
-        <v>46232</v>
-      </c>
-      <c r="F121" s="7"/>
-      <c r="G121" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="H121" s="6"/>
-      <c r="I121" s="6"/>
-      <c r="J121" s="6"/>
-      <c r="K121" s="6"/>
-      <c r="L121" s="6"/>
-      <c r="M121" s="6"/>
-      <c r="X121" s="30" t="s">
-        <v>326</v>
-      </c>
-      <c r="Y121" s="31">
-        <f>COUNTIFS(J:J,"in",L:L,AB75)</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="122" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="B122" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C122" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D122" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="E122" s="7"/>
-      <c r="F122" s="7">
-        <v>46218</v>
-      </c>
-      <c r="G122" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="H122" s="6"/>
-      <c r="I122" s="6"/>
-      <c r="J122" s="6"/>
-      <c r="K122" s="6"/>
-      <c r="L122" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M122" s="6" t="s">
-        <v>460</v>
-      </c>
-      <c r="U122" s="5"/>
-    </row>
-    <row r="123" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="B123" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="C123" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="D123" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E123" s="7"/>
-      <c r="F123" s="7">
-        <v>46221</v>
-      </c>
-      <c r="G123" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H123" s="6">
-        <v>5</v>
-      </c>
-      <c r="I123" s="6"/>
-      <c r="J123" s="6"/>
-      <c r="K123" s="6"/>
-      <c r="L123" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="M123" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="U123" s="5"/>
-    </row>
-    <row r="124" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="X124" s="32" t="s">
-        <v>327</v>
       </c>
       <c r="Y124" s="20">
         <f>COUNTIFS(J:J,"in",L:L,AB76,H:H,"&gt;0")</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="125" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="B125" s="6" t="s">
+        <v>471</v>
+      </c>
+      <c r="C125" s="6"/>
+      <c r="D125" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E125" s="7">
+        <v>46232</v>
+      </c>
+      <c r="F125" s="7"/>
+      <c r="G125" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="H125" s="6"/>
+      <c r="I125" s="6"/>
+      <c r="J125" s="6"/>
+      <c r="K125" s="6"/>
+      <c r="L125" s="6"/>
+      <c r="M125" s="6"/>
+      <c r="X125" s="30" t="s">
+        <v>326</v>
+      </c>
+      <c r="Y125" s="31">
+        <f>COUNTIFS(J:J,"in",L:L,AB78)</f>
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="B126" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C126" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D126" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E126" s="7"/>
+      <c r="F126" s="7">
+        <v>46218</v>
+      </c>
+      <c r="G126" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H126" s="6"/>
+      <c r="I126" s="6"/>
+      <c r="J126" s="6"/>
+      <c r="K126" s="6"/>
+      <c r="L126" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M126" s="6" t="s">
+        <v>460</v>
+      </c>
+      <c r="U126" s="5"/>
+    </row>
+    <row r="127" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="B127" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="C127" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E127" s="7"/>
+      <c r="F127" s="7">
+        <v>46221</v>
+      </c>
+      <c r="G127" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="H127" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="126" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="S126" t="s">
+      <c r="I127" s="6"/>
+      <c r="J127" s="6"/>
+      <c r="K127" s="6"/>
+      <c r="L127" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="M127" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="U127" s="5"/>
+    </row>
+    <row r="128" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="X128" s="32" t="s">
+        <v>327</v>
+      </c>
+      <c r="Y128" s="20">
+        <f>COUNTIFS(J:J,"in",L:L,AB79,H:H,"&gt;0")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" spans="19:20" x14ac:dyDescent="0.25">
+      <c r="S130" t="s">
         <v>455</v>
-      </c>
-    </row>
-    <row r="130" spans="19:20" x14ac:dyDescent="0.25">
-      <c r="S130" s="2">
-        <f>+MIN(I73:I113)</f>
-        <v>46209</v>
-      </c>
-      <c r="T130" s="37">
-        <f>SUMIFS(Q:Q,I:I,S130)</f>
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="131" spans="19:20" x14ac:dyDescent="0.25">
-      <c r="S131" s="2">
-        <f>+S130+1</f>
-        <v>46210</v>
-      </c>
-      <c r="T131" s="37">
-        <f>SUMIFS(Q:Q,I:I,S131)</f>
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="132" spans="19:20" x14ac:dyDescent="0.25">
-      <c r="S132" s="2">
-        <f t="shared" ref="S132:S157" si="0">+S131+1</f>
-        <v>46211</v>
-      </c>
-      <c r="T132" s="37">
-        <f>SUMIFS(Q:Q,I:I,S132)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="19:20" x14ac:dyDescent="0.25">
-      <c r="S133" s="2">
-        <f t="shared" si="0"/>
-        <v>46212</v>
-      </c>
-      <c r="T133" s="37">
-        <f>SUMIFS(Q:Q,I:I,S133)</f>
-        <v>0</v>
       </c>
     </row>
     <row r="134" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S134" s="2">
-        <f t="shared" si="0"/>
-        <v>46213</v>
+        <f>+MIN(I76:I116)</f>
+        <v>46209</v>
       </c>
       <c r="T134" s="37">
-        <f>SUMIFS(Q:Q,I:I,S134)</f>
-        <v>0</v>
+        <f t="shared" ref="T134:T165" si="0">SUMIFS(Q:Q,I:I,S134)</f>
+        <v>2000</v>
       </c>
     </row>
     <row r="135" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S135" s="2">
+        <f>+S134+1</f>
+        <v>46210</v>
+      </c>
+      <c r="T135" s="37">
         <f t="shared" si="0"/>
-        <v>46214</v>
-      </c>
-      <c r="T135" s="37">
-        <f>SUMIFS(Q:Q,I:I,S135)</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="136" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S136" s="2">
+        <f t="shared" ref="S136:S161" si="1">+S135+1</f>
+        <v>46211</v>
+      </c>
+      <c r="T136" s="37">
         <f t="shared" si="0"/>
-        <v>46215</v>
-      </c>
-      <c r="T136" s="37">
-        <f>SUMIFS(Q:Q,I:I,S136)</f>
-        <v>3500</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S137" s="2">
+        <f t="shared" si="1"/>
+        <v>46212</v>
+      </c>
+      <c r="T137" s="37">
         <f t="shared" si="0"/>
-        <v>46216</v>
-      </c>
-      <c r="T137" s="37">
-        <f>SUMIFS(Q:Q,I:I,S137)</f>
-        <v>2000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S138" s="2">
+        <f t="shared" si="1"/>
+        <v>46213</v>
+      </c>
+      <c r="T138" s="37">
         <f t="shared" si="0"/>
-        <v>46217</v>
-      </c>
-      <c r="T138" s="37">
-        <f>SUMIFS(Q:Q,I:I,S138)</f>
-        <v>4000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S139" s="2">
+        <f t="shared" si="1"/>
+        <v>46214</v>
+      </c>
+      <c r="T139" s="37">
         <f t="shared" si="0"/>
-        <v>46218</v>
-      </c>
-      <c r="T139" s="37">
-        <f>SUMIFS(Q:Q,I:I,S139)</f>
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S140" s="2">
+        <f t="shared" si="1"/>
+        <v>46215</v>
+      </c>
+      <c r="T140" s="37">
         <f t="shared" si="0"/>
-        <v>46219</v>
-      </c>
-      <c r="T140" s="37">
-        <f>SUMIFS(Q:Q,I:I,S140)</f>
-        <v>4000</v>
+        <v>3500</v>
       </c>
     </row>
     <row r="141" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S141" s="2">
+        <f t="shared" si="1"/>
+        <v>46216</v>
+      </c>
+      <c r="T141" s="37">
         <f t="shared" si="0"/>
-        <v>46220</v>
-      </c>
-      <c r="T141" s="37">
-        <f>SUMIFS(Q:Q,I:I,S141)</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="142" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S142" s="2">
+        <f t="shared" si="1"/>
+        <v>46217</v>
+      </c>
+      <c r="T142" s="37">
         <f t="shared" si="0"/>
-        <v>46221</v>
-      </c>
-      <c r="T142" s="37">
-        <f>SUMIFS(Q:Q,I:I,S142)</f>
-        <v>2000</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="143" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S143" s="2">
+        <f t="shared" si="1"/>
+        <v>46218</v>
+      </c>
+      <c r="T143" s="37">
         <f t="shared" si="0"/>
-        <v>46222</v>
-      </c>
-      <c r="T143" s="37">
-        <f>SUMIFS(Q:Q,I:I,S143)</f>
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="144" spans="19:20" x14ac:dyDescent="0.25">
       <c r="S144" s="2">
+        <f t="shared" si="1"/>
+        <v>46219</v>
+      </c>
+      <c r="T144" s="37">
         <f t="shared" si="0"/>
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="145" spans="19:20" x14ac:dyDescent="0.25">
+      <c r="S145" s="2">
+        <f t="shared" si="1"/>
+        <v>46220</v>
+      </c>
+      <c r="T145" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="19:20" x14ac:dyDescent="0.25">
+      <c r="S146" s="2">
+        <f t="shared" si="1"/>
+        <v>46221</v>
+      </c>
+      <c r="T146" s="37">
+        <f t="shared" si="0"/>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="147" spans="19:20" x14ac:dyDescent="0.25">
+      <c r="S147" s="2">
+        <f t="shared" si="1"/>
+        <v>46222</v>
+      </c>
+      <c r="T147" s="37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="19:20" x14ac:dyDescent="0.25">
+      <c r="S148" s="2">
+        <f t="shared" si="1"/>
         <v>46223</v>
       </c>
-      <c r="T144" s="37">
-        <f>SUMIFS(Q:Q,I:I,S144)</f>
+      <c r="T148" s="37">
+        <f t="shared" si="0"/>
         <v>6000</v>
       </c>
     </row>
-    <row r="145" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S145" s="2">
+    <row r="149" spans="19:20" x14ac:dyDescent="0.25">
+      <c r="S149" s="2">
+        <f t="shared" si="1"/>
+        <v>46224</v>
+      </c>
+      <c r="T149" s="37">
         <f t="shared" si="0"/>
-        <v>46224</v>
-      </c>
-      <c r="T145" s="37">
-        <f>SUMIFS(Q:Q,I:I,S145)</f>
         <v>2000</v>
       </c>
     </row>
-    <row r="146" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S146" s="2">
+    <row r="150" spans="19:20" x14ac:dyDescent="0.25">
+      <c r="S150" s="2">
+        <f t="shared" si="1"/>
+        <v>46225</v>
+      </c>
+      <c r="T150" s="37">
         <f t="shared" si="0"/>
-        <v>46225</v>
-      </c>
-      <c r="T146" s="37">
-        <f>SUMIFS(Q:Q,I:I,S146)</f>
         <v>4000</v>
       </c>
     </row>
-    <row r="147" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S147" s="2">
+    <row r="151" spans="19:20" x14ac:dyDescent="0.25">
+      <c r="S151" s="2">
+        <f t="shared" si="1"/>
+        <v>46226</v>
+      </c>
+      <c r="T151" s="37">
         <f t="shared" si="0"/>
-        <v>46226</v>
-      </c>
-      <c r="T147" s="37">
-        <f>SUMIFS(Q:Q,I:I,S147)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S148" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="19:20" x14ac:dyDescent="0.25">
+      <c r="S152" s="2">
+        <f t="shared" si="1"/>
+        <v>46227</v>
+      </c>
+      <c r="T152" s="37">
         <f t="shared" si="0"/>
-        <v>46227</v>
-      </c>
-      <c r="T148" s="37">
-        <f>SUMIFS(Q:Q,I:I,S148)</f>
         <v>4000</v>
       </c>
     </row>
-    <row r="149" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S149" s="2">
+    <row r="153" spans="19:20" x14ac:dyDescent="0.25">
+      <c r="S153" s="2">
+        <f t="shared" si="1"/>
+        <v>46228</v>
+      </c>
+      <c r="T153" s="37">
         <f t="shared" si="0"/>
-        <v>46228</v>
-      </c>
-      <c r="T149" s="37">
-        <f>SUMIFS(Q:Q,I:I,S149)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S150" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="19:20" x14ac:dyDescent="0.25">
+      <c r="S154" s="2">
+        <f t="shared" si="1"/>
+        <v>46229</v>
+      </c>
+      <c r="T154" s="37">
         <f t="shared" si="0"/>
-        <v>46229</v>
-      </c>
-      <c r="T150" s="37">
-        <f>SUMIFS(Q:Q,I:I,S150)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S151" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="19:20" x14ac:dyDescent="0.25">
+      <c r="S155" s="2">
+        <f t="shared" si="1"/>
+        <v>46230</v>
+      </c>
+      <c r="T155" s="37">
         <f t="shared" si="0"/>
-        <v>46230</v>
-      </c>
-      <c r="T151" s="37">
-        <f>SUMIFS(Q:Q,I:I,S151)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S152" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="19:20" x14ac:dyDescent="0.25">
+      <c r="S156" s="2">
+        <f t="shared" si="1"/>
+        <v>46231</v>
+      </c>
+      <c r="T156" s="37">
         <f t="shared" si="0"/>
-        <v>46231</v>
-      </c>
-      <c r="T152" s="37">
-        <f>SUMIFS(Q:Q,I:I,S152)</f>
         <v>2000</v>
       </c>
     </row>
-    <row r="153" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S153" s="2">
+    <row r="157" spans="19:20" x14ac:dyDescent="0.25">
+      <c r="S157" s="2">
+        <f t="shared" si="1"/>
+        <v>46232</v>
+      </c>
+      <c r="T157" s="37">
         <f t="shared" si="0"/>
-        <v>46232</v>
-      </c>
-      <c r="T153" s="37">
-        <f>SUMIFS(Q:Q,I:I,S153)</f>
         <v>2000</v>
       </c>
     </row>
-    <row r="154" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S154" s="2">
+    <row r="158" spans="19:20" x14ac:dyDescent="0.25">
+      <c r="S158" s="2">
+        <f t="shared" si="1"/>
+        <v>46233</v>
+      </c>
+      <c r="T158" s="37">
         <f t="shared" si="0"/>
-        <v>46233</v>
-      </c>
-      <c r="T154" s="37">
-        <f>SUMIFS(Q:Q,I:I,S154)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S155" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="19:20" x14ac:dyDescent="0.25">
+      <c r="S159" s="2">
+        <f t="shared" si="1"/>
+        <v>46234</v>
+      </c>
+      <c r="T159" s="37">
         <f t="shared" si="0"/>
-        <v>46234</v>
-      </c>
-      <c r="T155" s="37">
-        <f>SUMIFS(Q:Q,I:I,S155)</f>
         <v>6000</v>
       </c>
     </row>
-    <row r="156" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S156" s="2">
+    <row r="160" spans="19:20" x14ac:dyDescent="0.25">
+      <c r="S160" s="2">
+        <f t="shared" si="1"/>
+        <v>46235</v>
+      </c>
+      <c r="T160" s="37">
         <f t="shared" si="0"/>
-        <v>46235</v>
-      </c>
-      <c r="T156" s="37">
-        <f>SUMIFS(Q:Q,I:I,S156)</f>
         <v>3000</v>
       </c>
     </row>
-    <row r="157" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S157" s="2">
+    <row r="161" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S161" s="2">
+        <f t="shared" si="1"/>
+        <v>46236</v>
+      </c>
+      <c r="T161" s="37">
         <f t="shared" si="0"/>
-        <v>46236</v>
-      </c>
-      <c r="T157" s="37">
-        <f>SUMIFS(Q:Q,I:I,S157)</f>
-        <v>0</v>
-      </c>
-      <c r="V157">
+        <v>0</v>
+      </c>
+      <c r="V161">
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S158" s="2">
-        <f t="shared" ref="S158" si="1">+S157+1</f>
+    <row r="162" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S162" s="2">
+        <f t="shared" ref="S162:S165" si="2">+S161+1</f>
         <v>46237</v>
       </c>
-      <c r="T158" s="37">
-        <f>SUMIFS(Q:Q,I:I,S158)</f>
+      <c r="T162" s="37">
+        <f t="shared" si="0"/>
         <v>5000</v>
       </c>
     </row>
-    <row r="159" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="S159" s="2"/>
-      <c r="T159" s="37"/>
-      <c r="V159" s="40">
-        <f>+SUM(T135:T159)</f>
-        <v>54500</v>
-      </c>
-    </row>
-    <row r="160" spans="19:23" x14ac:dyDescent="0.25">
-      <c r="V160">
-        <f>+COUNT(S135:S159)</f>
-        <v>24</v>
-      </c>
-      <c r="W160">
-        <f>+V159/V160</f>
-        <v>2270.8333333333335</v>
+    <row r="163" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S163" s="2">
+        <f t="shared" si="2"/>
+        <v>46238</v>
+      </c>
+      <c r="T163" s="37">
+        <f t="shared" si="0"/>
+        <v>1000</v>
+      </c>
+      <c r="V163" s="40">
+        <f>+SUM(T139:T163)</f>
+        <v>55500</v>
       </c>
     </row>
     <row r="164" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S164" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="165" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="V165" s="50" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="166" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S166" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="T166" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="U166" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="V166" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="W166" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="X166" s="1" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="167" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S167" s="2">
-        <f t="shared" ref="S167:S172" si="2">+S168+1</f>
-        <v>46240</v>
-      </c>
-      <c r="T167">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S167)</f>
-        <v>1</v>
-      </c>
-      <c r="U167">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S167,entries!AE:AE,1)</f>
-        <v>1</v>
-      </c>
-      <c r="V167">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S167,entries!AF:AF,1)</f>
-        <v>0</v>
-      </c>
-      <c r="W167" s="37">
-        <v>2000</v>
-      </c>
-      <c r="X167" s="37">
-        <f>+AVERAGE(W168:W173)</f>
-        <v>2133.3333333333335</v>
-      </c>
-      <c r="Y167" s="40">
-        <f t="shared" ref="Y167:Y184" si="3">+AVERAGE(W167:W172)</f>
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="168" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S168" s="2">
+      <c r="S164" s="2">
         <f t="shared" si="2"/>
         <v>46239</v>
       </c>
-      <c r="T168">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S168)</f>
-        <v>0</v>
-      </c>
-      <c r="U168">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S168,entries!AE:AE,1)</f>
-        <v>0</v>
-      </c>
-      <c r="V168">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S168,entries!AF:AF,1)</f>
-        <v>0</v>
-      </c>
-      <c r="W168" s="37">
+      <c r="T164" s="37">
+        <f t="shared" si="0"/>
         <v>2000</v>
       </c>
-      <c r="X168" s="37">
-        <f>+AVERAGE(W169:W174)</f>
+      <c r="V164">
+        <f>+COUNT(S139:S163)</f>
+        <v>25</v>
+      </c>
+      <c r="W164">
+        <f>+V163/V164</f>
+        <v>2220</v>
+      </c>
+    </row>
+    <row r="165" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S165" s="2">
+        <f t="shared" si="2"/>
+        <v>46240</v>
+      </c>
+      <c r="T165" s="37">
+        <f t="shared" si="0"/>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="168" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S168" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="169" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="V169" s="50" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="170" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S170" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="T170" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="U170" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="V170" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="W170" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="X170" s="1" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="171" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S171" s="2">
+        <f t="shared" ref="S171:S176" si="3">+S172+1</f>
+        <v>46240</v>
+      </c>
+      <c r="T171">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S171)</f>
+        <v>1</v>
+      </c>
+      <c r="U171">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S171,entries!AE:AE,1)</f>
+        <v>1</v>
+      </c>
+      <c r="V171">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S171,entries!AF:AF,1)</f>
+        <v>0</v>
+      </c>
+      <c r="W171" s="37">
+        <v>2000</v>
+      </c>
+      <c r="X171" s="37">
+        <f>+AVERAGE(W172:W177)</f>
+        <v>2133.3333333333335</v>
+      </c>
+      <c r="Y171" s="40">
+        <f t="shared" ref="Y171:Y188" si="4">+AVERAGE(W171:W176)</f>
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="172" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S172" s="2">
+        <f t="shared" si="3"/>
+        <v>46239</v>
+      </c>
+      <c r="T172">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S172)</f>
+        <v>0</v>
+      </c>
+      <c r="U172">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S172,entries!AE:AE,1)</f>
+        <v>0</v>
+      </c>
+      <c r="V172">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S172,entries!AF:AF,1)</f>
+        <v>0</v>
+      </c>
+      <c r="W172" s="37">
+        <v>2000</v>
+      </c>
+      <c r="X172" s="37">
+        <f>+AVERAGE(W173:W178)</f>
         <v>2066.6666666666665</v>
       </c>
-      <c r="Y168" s="40">
+      <c r="Y172" s="40">
+        <f t="shared" si="4"/>
+        <v>2133.3333333333335</v>
+      </c>
+    </row>
+    <row r="173" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S173" s="2">
         <f t="shared" si="3"/>
-        <v>2133.3333333333335</v>
-      </c>
-    </row>
-    <row r="169" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S169" s="2">
-        <f t="shared" si="2"/>
         <v>46238</v>
       </c>
-      <c r="T169">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S169)</f>
+      <c r="T173">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S173)</f>
         <v>1</v>
       </c>
-      <c r="U169">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S169,entries!AE:AE,1)</f>
+      <c r="U173">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S173,entries!AE:AE,1)</f>
         <v>1</v>
       </c>
-      <c r="V169">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S169,entries!AF:AF,1)</f>
-        <v>0</v>
-      </c>
-      <c r="W169" s="37">
-        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$165,entries!G:G,S169)</f>
+      <c r="V173">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S173,entries!AF:AF,1)</f>
+        <v>0</v>
+      </c>
+      <c r="W173" s="37">
+        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$169,entries!G:G,S173)</f>
         <v>2000</v>
       </c>
-      <c r="X169" s="37">
-        <f t="shared" ref="X169:X183" si="4">+AVERAGE(W170:W175)</f>
+      <c r="X173" s="37">
+        <f t="shared" ref="X173:X187" si="5">+AVERAGE(W174:W179)</f>
         <v>2066.6666666666665</v>
       </c>
-      <c r="Y169" s="40">
+      <c r="Y173" s="40">
+        <f t="shared" si="4"/>
+        <v>2066.6666666666665</v>
+      </c>
+    </row>
+    <row r="174" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S174" s="2">
         <f t="shared" si="3"/>
+        <v>46237</v>
+      </c>
+      <c r="T174">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S174)</f>
+        <v>0</v>
+      </c>
+      <c r="U174">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S174,entries!AE:AE,1)</f>
+        <v>0</v>
+      </c>
+      <c r="V174">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S174,entries!AF:AF,1)</f>
+        <v>0</v>
+      </c>
+      <c r="W174" s="37">
+        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$169,entries!G:G,S174)</f>
+        <v>0</v>
+      </c>
+      <c r="X174" s="37">
+        <f t="shared" si="5"/>
+        <v>2400</v>
+      </c>
+      <c r="Y174" s="40">
+        <f t="shared" si="4"/>
         <v>2066.6666666666665</v>
       </c>
     </row>
-    <row r="170" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S170" s="2">
-        <f t="shared" si="2"/>
-        <v>46237</v>
-      </c>
-      <c r="T170">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S170)</f>
-        <v>0</v>
-      </c>
-      <c r="U170">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S170,entries!AE:AE,1)</f>
-        <v>0</v>
-      </c>
-      <c r="V170">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S170,entries!AF:AF,1)</f>
-        <v>0</v>
-      </c>
-      <c r="W170" s="37">
-        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$165,entries!G:G,S170)</f>
-        <v>0</v>
-      </c>
-      <c r="X170" s="37">
+    <row r="175" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S175" s="2">
+        <f t="shared" si="3"/>
+        <v>46236</v>
+      </c>
+      <c r="T175">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S175)</f>
+        <v>2</v>
+      </c>
+      <c r="U175">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S175,entries!AE:AE,1)</f>
+        <v>2</v>
+      </c>
+      <c r="V175">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S175,entries!AF:AF,1)</f>
+        <v>0</v>
+      </c>
+      <c r="W175" s="37">
+        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$169,entries!G:G,S175)</f>
+        <v>4000</v>
+      </c>
+      <c r="X175" s="37">
+        <f t="shared" si="5"/>
+        <v>1900</v>
+      </c>
+      <c r="Y175" s="40">
         <f t="shared" si="4"/>
         <v>2400</v>
       </c>
-      <c r="Y170" s="40">
+    </row>
+    <row r="176" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S176" s="2">
         <f t="shared" si="3"/>
-        <v>2066.6666666666665</v>
-      </c>
-    </row>
-    <row r="171" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S171" s="2">
-        <f t="shared" si="2"/>
-        <v>46236</v>
-      </c>
-      <c r="T171">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S171)</f>
-        <v>2</v>
-      </c>
-      <c r="U171">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S171,entries!AE:AE,1)</f>
-        <v>2</v>
-      </c>
-      <c r="V171">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S171,entries!AF:AF,1)</f>
-        <v>0</v>
-      </c>
-      <c r="W171" s="37">
-        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$165,entries!G:G,S171)</f>
-        <v>4000</v>
-      </c>
-      <c r="X171" s="37">
+        <v>46235</v>
+      </c>
+      <c r="T176">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S176)</f>
+        <v>1</v>
+      </c>
+      <c r="U176">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S176,entries!AE:AE,1)</f>
+        <v>1</v>
+      </c>
+      <c r="V176">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S176,entries!AF:AF,1)</f>
+        <v>0</v>
+      </c>
+      <c r="W176" s="37">
+        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$169,entries!G:G,S176)</f>
+        <v>2000</v>
+      </c>
+      <c r="X176" s="37">
+        <f t="shared" si="5"/>
+        <v>1900</v>
+      </c>
+      <c r="Y176" s="40">
         <f t="shared" si="4"/>
         <v>1900</v>
       </c>
-      <c r="Y171" s="40">
-        <f t="shared" si="3"/>
-        <v>2400</v>
-      </c>
-    </row>
-    <row r="172" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S172" s="2">
-        <f t="shared" si="2"/>
-        <v>46235</v>
-      </c>
-      <c r="T172">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S172)</f>
+    </row>
+    <row r="177" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S177" s="2">
+        <v>46234</v>
+      </c>
+      <c r="T177">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S177)</f>
+        <v>2</v>
+      </c>
+      <c r="U177">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S177,entries!AE:AE,1)</f>
         <v>1</v>
       </c>
-      <c r="U172">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S172,entries!AE:AE,1)</f>
+      <c r="V177">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S177,entries!AF:AF,1)</f>
         <v>1</v>
       </c>
-      <c r="V172">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S172,entries!AF:AF,1)</f>
-        <v>0</v>
-      </c>
-      <c r="W172" s="37">
-        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$165,entries!G:G,S172)</f>
-        <v>2000</v>
-      </c>
-      <c r="X172" s="37">
+      <c r="W177" s="37">
+        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$169,entries!G:G,S177)</f>
+        <v>2800</v>
+      </c>
+      <c r="X177" s="37">
+        <f t="shared" si="5"/>
+        <v>1766.6666666666667</v>
+      </c>
+      <c r="Y177" s="40">
         <f t="shared" si="4"/>
         <v>1900</v>
       </c>
-      <c r="Y172" s="40">
-        <f t="shared" si="3"/>
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="173" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S173" s="2">
-        <v>46234</v>
-      </c>
-      <c r="T173">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S173)</f>
+    </row>
+    <row r="178" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S178" s="2">
+        <v>46232</v>
+      </c>
+      <c r="T178">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S178)</f>
         <v>2</v>
       </c>
-      <c r="U173">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S173,entries!AE:AE,1)</f>
+      <c r="U178">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S178,entries!AE:AE,1)</f>
         <v>1</v>
       </c>
-      <c r="V173">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S173,entries!AF:AF,1)</f>
+      <c r="V178">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S178,entries!AF:AF,1)</f>
         <v>1</v>
       </c>
-      <c r="W173" s="37">
-        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$165,entries!G:G,S173)</f>
-        <v>2800</v>
-      </c>
-      <c r="X173" s="37">
+      <c r="W178" s="37">
+        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$169,entries!G:G,S178)</f>
+        <v>1600</v>
+      </c>
+      <c r="X178" s="37">
+        <f t="shared" si="5"/>
+        <v>1633.3333333333333</v>
+      </c>
+      <c r="Y178" s="40">
         <f t="shared" si="4"/>
         <v>1766.6666666666667</v>
       </c>
-      <c r="Y173" s="40">
-        <f t="shared" si="3"/>
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="174" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S174" s="2">
-        <v>46232</v>
-      </c>
-      <c r="T174">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S174)</f>
-        <v>2</v>
-      </c>
-      <c r="U174">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S174,entries!AE:AE,1)</f>
+    </row>
+    <row r="179" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S179" s="2">
+        <v>46231</v>
+      </c>
+      <c r="T179">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S179)</f>
         <v>1</v>
       </c>
-      <c r="V174">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S174,entries!AF:AF,1)</f>
+      <c r="U179">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S179,entries!AE:AE,1)</f>
         <v>1</v>
       </c>
-      <c r="W174" s="37">
-        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$165,entries!G:G,S174)</f>
-        <v>1600</v>
-      </c>
-      <c r="X174" s="37">
+      <c r="V179">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S179,entries!AF:AF,1)</f>
+        <v>0</v>
+      </c>
+      <c r="W179" s="37">
+        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$169,entries!G:G,S179)</f>
+        <v>2000</v>
+      </c>
+      <c r="X179" s="37">
+        <f t="shared" si="5"/>
+        <v>3100</v>
+      </c>
+      <c r="Y179" s="40">
         <f t="shared" si="4"/>
         <v>1633.3333333333333</v>
       </c>
-      <c r="Y174" s="40">
-        <f t="shared" si="3"/>
-        <v>1766.6666666666667</v>
-      </c>
-    </row>
-    <row r="175" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S175" s="2">
-        <v>46231</v>
-      </c>
-      <c r="T175">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S175)</f>
+    </row>
+    <row r="180" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S180" s="2">
+        <v>46230</v>
+      </c>
+      <c r="T180">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S180)</f>
         <v>1</v>
       </c>
-      <c r="U175">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S175,entries!AE:AE,1)</f>
+      <c r="U180">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S180,entries!AE:AE,1)</f>
         <v>1</v>
       </c>
-      <c r="V175">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S175,entries!AF:AF,1)</f>
-        <v>0</v>
-      </c>
-      <c r="W175" s="37">
-        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$165,entries!G:G,S175)</f>
+      <c r="V180">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S180,entries!AF:AF,1)</f>
+        <v>0</v>
+      </c>
+      <c r="W180" s="37">
+        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$169,entries!G:G,S180)</f>
         <v>2000</v>
       </c>
-      <c r="X175" s="37">
+      <c r="X180" s="37">
+        <f t="shared" si="5"/>
+        <v>2900</v>
+      </c>
+      <c r="Y180" s="40">
         <f t="shared" si="4"/>
         <v>3100</v>
       </c>
-      <c r="Y175" s="40">
-        <f t="shared" si="3"/>
-        <v>1633.3333333333333</v>
-      </c>
-    </row>
-    <row r="176" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S176" s="2">
-        <v>46230</v>
-      </c>
-      <c r="T176">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S176)</f>
+    </row>
+    <row r="181" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S181" s="2">
+        <v>46229</v>
+      </c>
+      <c r="T181">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S181)</f>
         <v>1</v>
       </c>
-      <c r="U176">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S176,entries!AE:AE,1)</f>
+      <c r="U181">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S181,entries!AE:AE,1)</f>
         <v>1</v>
       </c>
-      <c r="V176">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S176,entries!AF:AF,1)</f>
-        <v>0</v>
-      </c>
-      <c r="W176" s="37">
-        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$165,entries!G:G,S176)</f>
-        <v>2000</v>
-      </c>
-      <c r="X176" s="37">
+      <c r="V181">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S181,entries!AF:AF,1)</f>
+        <v>0</v>
+      </c>
+      <c r="W181" s="37">
+        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$169,entries!G:G,S181)</f>
+        <v>1000</v>
+      </c>
+      <c r="X181" s="37">
+        <f t="shared" si="5"/>
+        <v>3066.6666666666665</v>
+      </c>
+      <c r="Y181" s="40">
         <f t="shared" si="4"/>
         <v>2900</v>
       </c>
-      <c r="Y176" s="40">
-        <f t="shared" si="3"/>
-        <v>3100</v>
-      </c>
-    </row>
-    <row r="177" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S177" s="2">
-        <v>46229</v>
-      </c>
-      <c r="T177">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S177)</f>
+    </row>
+    <row r="182" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S182" s="2">
+        <v>46228</v>
+      </c>
+      <c r="T182">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S182)</f>
         <v>1</v>
       </c>
-      <c r="U177">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S177,entries!AE:AE,1)</f>
+      <c r="U182">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S182,entries!AE:AE,1)</f>
         <v>1</v>
       </c>
-      <c r="V177">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S177,entries!AF:AF,1)</f>
-        <v>0</v>
-      </c>
-      <c r="W177" s="37">
-        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$165,entries!G:G,S177)</f>
-        <v>1000</v>
-      </c>
-      <c r="X177" s="37">
+      <c r="V182">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S182,entries!AF:AF,1)</f>
+        <v>0</v>
+      </c>
+      <c r="W182" s="37">
+        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$169,entries!G:G,S182)</f>
+        <v>2000</v>
+      </c>
+      <c r="X182" s="37">
+        <f t="shared" si="5"/>
+        <v>3066.6666666666665</v>
+      </c>
+      <c r="Y182" s="40">
         <f t="shared" si="4"/>
         <v>3066.6666666666665</v>
       </c>
-      <c r="Y177" s="40">
-        <f t="shared" si="3"/>
-        <v>2900</v>
-      </c>
-    </row>
-    <row r="178" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S178" s="2">
-        <v>46228</v>
-      </c>
-      <c r="T178">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S178)</f>
+    </row>
+    <row r="183" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S183" s="2">
+        <v>46226</v>
+      </c>
+      <c r="T183">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S183)</f>
         <v>1</v>
       </c>
-      <c r="U178">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S178,entries!AE:AE,1)</f>
+      <c r="U183">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S183,entries!AE:AE,1)</f>
         <v>1</v>
       </c>
-      <c r="V178">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S178,entries!AF:AF,1)</f>
-        <v>0</v>
-      </c>
-      <c r="W178" s="37">
-        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$165,entries!G:G,S178)</f>
+      <c r="V183">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S183,entries!AF:AF,1)</f>
+        <v>0</v>
+      </c>
+      <c r="W183" s="37">
+        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$169,entries!G:G,S183)</f>
         <v>2000</v>
       </c>
-      <c r="X178" s="37">
+      <c r="X183" s="37">
+        <f t="shared" si="5"/>
+        <v>3066.6666666666665</v>
+      </c>
+      <c r="Y183" s="40">
         <f t="shared" si="4"/>
         <v>3066.6666666666665</v>
       </c>
-      <c r="Y178" s="40">
-        <f t="shared" si="3"/>
-        <v>3066.6666666666665</v>
-      </c>
-    </row>
-    <row r="179" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S179" s="2">
-        <v>46226</v>
-      </c>
-      <c r="T179">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S179)</f>
+    </row>
+    <row r="184" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S184" s="2">
+        <v>46224</v>
+      </c>
+      <c r="T184">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S184)</f>
         <v>1</v>
       </c>
-      <c r="U179">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S179,entries!AE:AE,1)</f>
+      <c r="U184">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S184,entries!AE:AE,1)</f>
+        <v>0</v>
+      </c>
+      <c r="V184">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S184,entries!AF:AF,1)</f>
         <v>1</v>
       </c>
-      <c r="V179">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S179,entries!AF:AF,1)</f>
-        <v>0</v>
-      </c>
-      <c r="W179" s="37">
-        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$165,entries!G:G,S179)</f>
-        <v>2000</v>
-      </c>
-      <c r="X179" s="37">
+      <c r="W184" s="37">
+        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$169,entries!G:G,S184)</f>
+        <v>800</v>
+      </c>
+      <c r="X184" s="37">
+        <f t="shared" si="5"/>
+        <v>3266.6666666666665</v>
+      </c>
+      <c r="Y184" s="40">
         <f t="shared" si="4"/>
         <v>3066.6666666666665</v>
       </c>
-      <c r="Y179" s="40">
-        <f t="shared" si="3"/>
-        <v>3066.6666666666665</v>
-      </c>
-    </row>
-    <row r="180" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S180" s="2">
-        <v>46224</v>
-      </c>
-      <c r="T180">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S180)</f>
-        <v>1</v>
-      </c>
-      <c r="U180">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S180,entries!AE:AE,1)</f>
-        <v>0</v>
-      </c>
-      <c r="V180">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S180,entries!AF:AF,1)</f>
-        <v>1</v>
-      </c>
-      <c r="W180" s="37">
-        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$165,entries!G:G,S180)</f>
-        <v>800</v>
-      </c>
-      <c r="X180" s="37">
+    </row>
+    <row r="185" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S185" s="2">
+        <v>46223</v>
+      </c>
+      <c r="T185">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S185)</f>
+        <v>6</v>
+      </c>
+      <c r="U185">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S185,entries!AE:AE,1)</f>
+        <v>3</v>
+      </c>
+      <c r="V185">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S185,entries!AF:AF,1)</f>
+        <v>3</v>
+      </c>
+      <c r="W185" s="37">
+        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$169,entries!G:G,S185)</f>
+        <v>10800</v>
+      </c>
+      <c r="X185" s="37">
+        <f t="shared" si="5"/>
+        <v>1733.3333333333333</v>
+      </c>
+      <c r="Y185" s="40">
         <f t="shared" si="4"/>
         <v>3266.6666666666665</v>
       </c>
-      <c r="Y180" s="40">
-        <f t="shared" si="3"/>
-        <v>3066.6666666666665</v>
-      </c>
-    </row>
-    <row r="181" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S181" s="2">
-        <v>46223</v>
-      </c>
-      <c r="T181">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S181)</f>
-        <v>6</v>
-      </c>
-      <c r="U181">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S181,entries!AE:AE,1)</f>
-        <v>3</v>
-      </c>
-      <c r="V181">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S181,entries!AF:AF,1)</f>
-        <v>3</v>
-      </c>
-      <c r="W181" s="37">
-        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$165,entries!G:G,S181)</f>
-        <v>10800</v>
-      </c>
-      <c r="X181" s="37">
+    </row>
+    <row r="186" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S186" s="2">
+        <v>46222</v>
+      </c>
+      <c r="T186">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S186)</f>
+        <v>1</v>
+      </c>
+      <c r="U186">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S186,entries!AE:AE,1)</f>
+        <v>0</v>
+      </c>
+      <c r="V186">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S186,entries!AF:AF,1)</f>
+        <v>1</v>
+      </c>
+      <c r="W186" s="37">
+        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$169,entries!G:G,S186)</f>
+        <v>800</v>
+      </c>
+      <c r="X186" s="37">
+        <f t="shared" si="5"/>
+        <v>2933.3333333333335</v>
+      </c>
+      <c r="Y186" s="40">
         <f t="shared" si="4"/>
         <v>1733.3333333333333</v>
       </c>
-      <c r="Y181" s="40">
-        <f t="shared" si="3"/>
-        <v>3266.6666666666665</v>
-      </c>
-    </row>
-    <row r="182" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S182" s="2">
-        <v>46222</v>
-      </c>
-      <c r="T182">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S182)</f>
+    </row>
+    <row r="187" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S187" s="2">
+        <v>46221</v>
+      </c>
+      <c r="T187">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S187)</f>
         <v>1</v>
       </c>
-      <c r="U182">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S182,entries!AE:AE,1)</f>
-        <v>0</v>
-      </c>
-      <c r="V182">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S182,entries!AF:AF,1)</f>
+      <c r="U187">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S187,entries!AE:AE,1)</f>
+        <v>0</v>
+      </c>
+      <c r="V187">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S187,entries!AF:AF,1)</f>
         <v>1</v>
       </c>
-      <c r="W182" s="37">
-        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$165,entries!G:G,S182)</f>
-        <v>800</v>
-      </c>
-      <c r="X182" s="37">
+      <c r="W187" s="37">
+        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$169,entries!G:G,S187)</f>
+        <v>2000</v>
+      </c>
+      <c r="X187" s="37">
+        <f t="shared" si="5"/>
+        <v>3600</v>
+      </c>
+      <c r="Y187" s="40">
         <f t="shared" si="4"/>
         <v>2933.3333333333335</v>
       </c>
-      <c r="Y182" s="40">
-        <f t="shared" si="3"/>
-        <v>1733.3333333333333</v>
-      </c>
-    </row>
-    <row r="183" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S183" s="2">
-        <v>46221</v>
-      </c>
-      <c r="T183">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S183)</f>
+    </row>
+    <row r="188" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S188" s="2">
+        <v>46220</v>
+      </c>
+      <c r="T188">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S188)</f>
         <v>1</v>
       </c>
-      <c r="U183">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S183,entries!AE:AE,1)</f>
-        <v>0</v>
-      </c>
-      <c r="V183">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S183,entries!AF:AF,1)</f>
+      <c r="U188">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S188,entries!AE:AE,1)</f>
         <v>1</v>
       </c>
-      <c r="W183" s="37">
-        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$165,entries!G:G,S183)</f>
+      <c r="V188">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S188,entries!AF:AF,1)</f>
+        <v>0</v>
+      </c>
+      <c r="W188" s="37">
+        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$169,entries!G:G,S188)</f>
         <v>2000</v>
       </c>
-      <c r="X183" s="37">
+      <c r="X188" s="37"/>
+      <c r="Y188" s="40">
         <f t="shared" si="4"/>
         <v>3600</v>
       </c>
-      <c r="Y183" s="40">
-        <f t="shared" si="3"/>
-        <v>2933.3333333333335</v>
-      </c>
-    </row>
-    <row r="184" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S184" s="2">
-        <v>46220</v>
-      </c>
-      <c r="T184">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S184)</f>
-        <v>1</v>
-      </c>
-      <c r="U184">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S184,entries!AE:AE,1)</f>
-        <v>1</v>
-      </c>
-      <c r="V184">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S184,entries!AF:AF,1)</f>
-        <v>0</v>
-      </c>
-      <c r="W184" s="37">
-        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$165,entries!G:G,S184)</f>
-        <v>2000</v>
-      </c>
-      <c r="X184" s="37"/>
-      <c r="Y184" s="40">
-        <f t="shared" si="3"/>
-        <v>3600</v>
-      </c>
-    </row>
-    <row r="185" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S185" s="2">
-        <v>46219</v>
-      </c>
-      <c r="T185">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S185)</f>
-        <v>1</v>
-      </c>
-      <c r="U185">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S185,entries!AE:AE,1)</f>
-        <v>0</v>
-      </c>
-      <c r="V185">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S185,entries!AF:AF,1)</f>
-        <v>1</v>
-      </c>
-      <c r="W185" s="37">
-        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$165,entries!G:G,S185)</f>
-        <v>2000</v>
-      </c>
-      <c r="X185" s="37"/>
-    </row>
-    <row r="186" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S186" s="2">
-        <v>46218</v>
-      </c>
-      <c r="T186">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S186)</f>
-        <v>1</v>
-      </c>
-      <c r="U186">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S186,entries!AE:AE,1)</f>
-        <v>1</v>
-      </c>
-      <c r="V186">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S186,entries!AF:AF,1)</f>
-        <v>0</v>
-      </c>
-      <c r="W186" s="37">
-        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$165,entries!G:G,S186)</f>
-        <v>2000</v>
-      </c>
-      <c r="X186" s="37"/>
-    </row>
-    <row r="187" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S187" s="2">
-        <v>46217</v>
-      </c>
-      <c r="T187">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S187)</f>
-        <v>2</v>
-      </c>
-      <c r="U187">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S187,entries!AE:AE,1)</f>
-        <v>1</v>
-      </c>
-      <c r="V187">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S187,entries!AF:AF,1)</f>
-        <v>1</v>
-      </c>
-      <c r="W187" s="37">
-        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$165,entries!G:G,S187)</f>
-        <v>1600</v>
-      </c>
-      <c r="X187" s="37"/>
-    </row>
-    <row r="188" spans="19:25" x14ac:dyDescent="0.25">
-      <c r="S188" s="2">
-        <v>46216</v>
-      </c>
-      <c r="T188">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S188)</f>
-        <v>4</v>
-      </c>
-      <c r="U188">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S188,entries!AE:AE,1)</f>
-        <v>2</v>
-      </c>
-      <c r="V188">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S188,entries!AF:AF,1)</f>
-        <v>2</v>
-      </c>
-      <c r="W188" s="37">
-        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$165,entries!G:G,S188)</f>
-        <v>8000</v>
-      </c>
-      <c r="X188" s="37"/>
     </row>
     <row r="189" spans="19:25" x14ac:dyDescent="0.25">
       <c r="S189" s="2">
+        <v>46219</v>
+      </c>
+      <c r="T189">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S189)</f>
+        <v>1</v>
+      </c>
+      <c r="U189">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S189,entries!AE:AE,1)</f>
+        <v>0</v>
+      </c>
+      <c r="V189">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S189,entries!AF:AF,1)</f>
+        <v>1</v>
+      </c>
+      <c r="W189" s="37">
+        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$169,entries!G:G,S189)</f>
+        <v>2000</v>
+      </c>
+      <c r="X189" s="37"/>
+    </row>
+    <row r="190" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S190" s="2">
+        <v>46218</v>
+      </c>
+      <c r="T190">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S190)</f>
+        <v>1</v>
+      </c>
+      <c r="U190">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S190,entries!AE:AE,1)</f>
+        <v>1</v>
+      </c>
+      <c r="V190">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S190,entries!AF:AF,1)</f>
+        <v>0</v>
+      </c>
+      <c r="W190" s="37">
+        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$169,entries!G:G,S190)</f>
+        <v>2000</v>
+      </c>
+      <c r="X190" s="37"/>
+    </row>
+    <row r="191" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S191" s="2">
+        <v>46217</v>
+      </c>
+      <c r="T191">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S191)</f>
+        <v>2</v>
+      </c>
+      <c r="U191">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S191,entries!AE:AE,1)</f>
+        <v>1</v>
+      </c>
+      <c r="V191">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S191,entries!AF:AF,1)</f>
+        <v>1</v>
+      </c>
+      <c r="W191" s="37">
+        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$169,entries!G:G,S191)</f>
+        <v>1600</v>
+      </c>
+      <c r="X191" s="37"/>
+    </row>
+    <row r="192" spans="19:25" x14ac:dyDescent="0.25">
+      <c r="S192" s="2">
+        <v>46216</v>
+      </c>
+      <c r="T192">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S192)</f>
+        <v>4</v>
+      </c>
+      <c r="U192">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S192,entries!AE:AE,1)</f>
+        <v>2</v>
+      </c>
+      <c r="V192">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S192,entries!AF:AF,1)</f>
+        <v>2</v>
+      </c>
+      <c r="W192" s="37">
+        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$169,entries!G:G,S192)</f>
+        <v>8000</v>
+      </c>
+      <c r="X192" s="37"/>
+    </row>
+    <row r="193" spans="19:24" x14ac:dyDescent="0.25">
+      <c r="S193" s="2">
         <v>46215</v>
       </c>
-      <c r="T189">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S189)</f>
+      <c r="T193">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S193)</f>
         <v>3</v>
       </c>
-      <c r="U189">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S189,entries!AE:AE,1)</f>
+      <c r="U193">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S193,entries!AE:AE,1)</f>
         <v>3</v>
       </c>
-      <c r="V189">
-        <f>+COUNTIFS(entries!V:V,$V$165,entries!G:G,S189,entries!AF:AF,1)</f>
-        <v>0</v>
-      </c>
-      <c r="W189" s="37">
-        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$165,entries!G:G,S189)</f>
+      <c r="V193">
+        <f>+COUNTIFS(entries!V:V,$V$169,entries!G:G,S193,entries!AF:AF,1)</f>
+        <v>0</v>
+      </c>
+      <c r="W193" s="37">
+        <f>+SUMIFS(entries!AG:AG,entries!V:V,$V$169,entries!G:G,S193)</f>
         <v>6000</v>
       </c>
-      <c r="X189" s="37"/>
+      <c r="X193" s="37"/>
     </row>
   </sheetData>
-  <autoFilter ref="B2:N70" xr:uid="{8D528AF1-A5E7-4779-9634-4965A885E745}">
+  <autoFilter ref="B2:N71" xr:uid="{8D528AF1-A5E7-4779-9634-4965A885E745}">
     <filterColumn colId="8">
       <filters>
         <filter val="in"/>
@@ -12428,6 +12667,96 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64544564-F30C-4E77-A14D-C4D6E7465882}">
+  <dimension ref="B3:F7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="3" width="22.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>537</v>
+      </c>
+      <c r="C3" t="s">
+        <v>538</v>
+      </c>
+      <c r="D3" t="s">
+        <v>535</v>
+      </c>
+      <c r="E3" t="s">
+        <v>536</v>
+      </c>
+      <c r="F3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="2">
+        <v>46242</v>
+      </c>
+      <c r="D4" t="s">
+        <v>533</v>
+      </c>
+      <c r="E4" t="s">
+        <v>534</v>
+      </c>
+      <c r="F4" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5" s="2">
+        <v>46242</v>
+      </c>
+      <c r="D5" t="s">
+        <v>287</v>
+      </c>
+      <c r="E5" t="s">
+        <v>532</v>
+      </c>
+      <c r="F5" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="2"/>
+      <c r="D6" t="s">
+        <v>542</v>
+      </c>
+      <c r="E6" t="s">
+        <v>532</v>
+      </c>
+      <c r="F6" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>342</v>
+      </c>
+      <c r="C7" s="2">
+        <v>46243</v>
+      </c>
+      <c r="F7" t="s">
+        <v>540</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{57273964-4986-4100-9546-DE01853A793F}">
   <dimension ref="B3:S56"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14019,7 +14348,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5894567E-3661-4FF2-878F-6408B0BD57B7}">
   <dimension ref="C7:I22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -14324,7 +14653,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{108150AC-C6AD-4AA2-B41E-842C5906F98B}">
   <dimension ref="A5:AF21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -16033,7 +16362,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A8439AE-98F9-4521-A527-9D099EC54153}">
   <dimension ref="C7:Q63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -16874,13 +17203,13 @@
     </row>
     <row r="60" spans="3:17" x14ac:dyDescent="0.25">
       <c r="O60" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="P60" s="1" t="s">
         <v>524</v>
       </c>
-      <c r="P60" s="1" t="s">
+      <c r="Q60" s="1" t="s">
         <v>525</v>
-      </c>
-      <c r="Q60" s="1" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="61" spans="3:17" x14ac:dyDescent="0.25">
@@ -16927,7 +17256,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EA84E51-DEFE-437C-880A-5EA971490775}">
   <dimension ref="A1:AG37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -17036,12 +17365,12 @@
         <v>500</v>
       </c>
       <c r="AG1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C2">
         <v>9856074</v>
@@ -17071,7 +17400,7 @@
         <v>236</v>
       </c>
       <c r="M2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="N2" t="s">
         <v>254</v>
@@ -17229,7 +17558,7 @@
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C4">
         <v>9514561</v>
@@ -17259,13 +17588,13 @@
         <v>236</v>
       </c>
       <c r="M4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="N4" t="s">
         <v>254</v>
       </c>
       <c r="O4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="P4" t="s">
         <v>238</v>
@@ -17331,7 +17660,7 @@
         <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F5" t="s">
         <v>232</v>
@@ -17424,7 +17753,7 @@
         <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F6" t="s">
         <v>232</v>
@@ -20379,7 +20708,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F1BE89C-ED98-4FE8-9366-064694B2838B}">
   <dimension ref="C2:U19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -20392,10 +20721,10 @@
   <sheetData>
     <row r="2" spans="3:4" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="D2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="3" spans="3:4" x14ac:dyDescent="0.25">
